--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="1054">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3180,6 +3180,12 @@
   </si>
   <si>
     <t>Durand's Legacy</t>
+  </si>
+  <si>
+    <t>Aegis Frame</t>
+  </si>
+  <si>
+    <t>Revenant Reign</t>
   </si>
 </sst>
 </file>
@@ -4834,6 +4840,9 @@
       <c r="D24" s="13" t="s">
         <v>977</v>
       </c>
+      <c r="E24" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="T24" s="41"/>
       <c r="U24" s="41"/>
       <c r="V24" s="41"/>
@@ -5674,6 +5683,9 @@
       </c>
       <c r="K41" s="9" t="s">
         <v>900</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>1052</v>
       </c>
       <c r="T41" s="41"/>
       <c r="U41" s="41"/>
@@ -8448,6 +8460,9 @@
       <c r="F102" s="11" t="s">
         <v>955</v>
       </c>
+      <c r="G102" s="1" t="s">
+        <v>1052</v>
+      </c>
       <c r="T102" s="41"/>
       <c r="U102" s="41"/>
       <c r="V102" s="41"/>
@@ -9096,6 +9111,9 @@
       <c r="G118" s="8" t="s">
         <v>1016</v>
       </c>
+      <c r="H118" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="T118" s="41"/>
       <c r="U118" s="41"/>
       <c r="V118" s="41"/>
@@ -10747,6 +10765,9 @@
       </c>
       <c r="H155" s="8" t="s">
         <v>990</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>1053</v>
       </c>
       <c r="T155" s="41"/>
       <c r="U155" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="1054">
   <si>
     <t>Aatrox</t>
   </si>
@@ -5232,6 +5232,9 @@
       <c r="O32" s="13" t="s">
         <v>1024</v>
       </c>
+      <c r="P32" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="T32" s="41"/>
       <c r="U32" s="41"/>
       <c r="V32" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2213" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="1054">
   <si>
     <t>Aatrox</t>
   </si>
@@ -4546,7 +4546,9 @@
       <c r="U15" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="V15" s="41"/>
+      <c r="V15" s="41" t="s">
+        <v>432</v>
+      </c>
       <c r="W15" s="2"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
@@ -4909,7 +4911,9 @@
       <c r="T25" s="47" t="s">
         <v>1003</v>
       </c>
-      <c r="U25" s="41"/>
+      <c r="U25" s="41" t="s">
+        <v>432</v>
+      </c>
       <c r="V25" s="41"/>
       <c r="W25" s="2"/>
     </row>
@@ -8565,6 +8569,9 @@
       <c r="N104" s="10" t="s">
         <v>821</v>
       </c>
+      <c r="O104" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="T104" s="41"/>
       <c r="U104" s="41"/>
       <c r="V104" s="41"/>
@@ -9245,6 +9252,9 @@
       </c>
       <c r="K121" s="8" t="s">
         <v>976</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="T121" s="41"/>
       <c r="U121" s="41"/>
@@ -11334,6 +11344,9 @@
       <c r="K168" s="1" t="s">
         <v>224</v>
       </c>
+      <c r="L168" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="T168" s="41"/>
       <c r="U168" s="41"/>
       <c r="V168" s="41"/>
@@ -11515,6 +11528,9 @@
       <c r="M173" s="12" t="s">
         <v>933</v>
       </c>
+      <c r="N173" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="T173" s="41"/>
       <c r="U173" s="41"/>
       <c r="V173" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="1056">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3186,6 +3186,12 @@
   </si>
   <si>
     <t>Revenant Reign</t>
+  </si>
+  <si>
+    <t>Petals of Spring</t>
+  </si>
+  <si>
+    <t>Divine Architect Porcelain</t>
   </si>
 </sst>
 </file>
@@ -4573,6 +4579,9 @@
       <c r="G16" s="9" t="s">
         <v>822</v>
       </c>
+      <c r="H16" s="1" t="s">
+        <v>1055</v>
+      </c>
       <c r="T16" s="41"/>
       <c r="U16" s="41"/>
       <c r="V16" s="41"/>
@@ -4945,6 +4954,9 @@
       <c r="I26" s="8" t="s">
         <v>898</v>
       </c>
+      <c r="J26" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="T26" s="41"/>
       <c r="U26" s="41"/>
       <c r="V26" s="41"/>
@@ -6408,6 +6420,9 @@
       <c r="M57" s="6" t="s">
         <v>1004</v>
       </c>
+      <c r="N57" s="1" t="s">
+        <v>1054</v>
+      </c>
       <c r="T57" s="41"/>
       <c r="U57" s="41"/>
       <c r="V57" s="41"/>
@@ -6798,7 +6813,9 @@
       <c r="T65" s="48" t="s">
         <v>1017</v>
       </c>
-      <c r="U65" s="41"/>
+      <c r="U65" s="41" t="s">
+        <v>1054</v>
+      </c>
       <c r="V65" s="41"/>
       <c r="W65" s="2"/>
     </row>
@@ -7315,6 +7332,9 @@
       </c>
       <c r="G77" s="1" t="s">
         <v>1038</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>1054</v>
       </c>
       <c r="T77" s="41"/>
       <c r="U77" s="41"/>
@@ -11199,7 +11219,9 @@
       <c r="S164" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="T164" s="41"/>
+      <c r="T164" s="41" t="s">
+        <v>1054</v>
+      </c>
       <c r="U164" s="41"/>
       <c r="V164" s="41"/>
       <c r="W164" s="2"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -2414,9 +2414,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>F-</t>
-  </si>
-  <si>
     <t>Giant Enemy Crabgot</t>
   </si>
   <si>
@@ -3192,6 +3189,9 @@
   </si>
   <si>
     <t>Divine Architect Porcelain</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -3419,7 +3419,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3583,6 +3583,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Eingabe" xfId="1" builtinId="20"/>
@@ -3592,15 +3595,15 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFF9933"/>
+      <color rgb="FF0099CC"/>
+      <color rgb="FF00FFCC"/>
       <color rgb="FF00CC66"/>
       <color rgb="FF66FF33"/>
-      <color rgb="FF00FFCC"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFF9933"/>
+      <color rgb="FFCCFF33"/>
       <color rgb="FFFFCC00"/>
-      <color rgb="FFCCFF33"/>
-      <color rgb="FF0099CC"/>
       <color rgb="FFFFC000"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF7030A0"/>
     </mruColors>
   </colors>
@@ -3933,7 +3936,7 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>785</v>
@@ -3966,7 +3969,7 @@
         <v>795</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>796</v>
+        <v>1055</v>
       </c>
       <c r="M2" s="34" t="s">
         <v>793</v>
@@ -4024,7 +4027,7 @@
         <v>161</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>162</v>
@@ -4036,13 +4039,13 @@
         <v>500</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>919</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>920</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="Q5" s="37"/>
       <c r="T5" s="37"/>
@@ -4085,7 +4088,7 @@
         <v>171</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>172</v>
@@ -4103,19 +4106,19 @@
         <v>278</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="S6" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="T6" s="48" t="s">
         <v>970</v>
       </c>
-      <c r="T6" s="48" t="s">
-        <v>971</v>
-      </c>
-      <c r="U6" s="41" t="s">
+      <c r="U6" s="44" t="s">
+        <v>1033</v>
+      </c>
+      <c r="V6" s="47" t="s">
         <v>1034</v>
-      </c>
-      <c r="V6" s="41" t="s">
-        <v>1035</v>
       </c>
       <c r="W6" s="2"/>
     </row>
@@ -4154,7 +4157,7 @@
         <v>171</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>183</v>
@@ -4166,31 +4169,31 @@
         <v>175</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>170</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>276</v>
       </c>
       <c r="T7" s="42" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="U7" s="47" t="s">
-        <v>895</v>
-      </c>
-      <c r="V7" s="41" t="s">
+        <v>894</v>
+      </c>
+      <c r="V7" s="42" t="s">
         <v>173</v>
       </c>
       <c r="W7" s="2"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>157</v>
@@ -4202,7 +4205,7 @@
         <v>675</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="T8" s="41"/>
       <c r="U8" s="41"/>
@@ -4258,7 +4261,7 @@
       <c r="P9" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9" s="6" t="s">
         <v>172</v>
       </c>
       <c r="T9" s="41"/>
@@ -4267,13 +4270,13 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>997</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>998</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="45"/>
@@ -4334,13 +4337,13 @@
         <v>206</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="T11" s="41"/>
       <c r="U11" s="41"/>
@@ -4382,10 +4385,10 @@
         <v>213</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>162</v>
@@ -4421,7 +4424,7 @@
         <v>219</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>220</v>
@@ -4442,16 +4445,16 @@
         <v>197</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="T13" s="41"/>
       <c r="U13" s="41"/>
@@ -4472,16 +4475,16 @@
         <v>197</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>173</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>937</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>1036</v>
+        <v>936</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>1035</v>
       </c>
       <c r="T14" s="41"/>
       <c r="U14" s="41"/>
@@ -4520,7 +4523,7 @@
         <v>183</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>231</v>
@@ -4535,16 +4538,16 @@
         <v>276</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>509</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="T15" s="47" t="s">
         <v>177</v>
@@ -4552,7 +4555,7 @@
       <c r="U15" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="V15" s="41" t="s">
+      <c r="V15" s="49" t="s">
         <v>432</v>
       </c>
       <c r="W15" s="2"/>
@@ -4574,13 +4577,13 @@
         <v>235</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>822</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>1055</v>
+        <v>821</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>1054</v>
       </c>
       <c r="T16" s="41"/>
       <c r="U16" s="41"/>
@@ -4589,7 +4592,7 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>157</v>
@@ -4597,7 +4600,7 @@
       <c r="C17" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="8" t="s">
         <v>278</v>
       </c>
       <c r="E17" s="45"/>
@@ -4630,10 +4633,10 @@
         <v>172</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="T18" s="41"/>
       <c r="U18" s="41"/>
@@ -4660,13 +4663,13 @@
         <v>240</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>430</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>173</v>
@@ -4678,7 +4681,7 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>157</v>
@@ -4687,10 +4690,10 @@
         <v>248</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="T20" s="41"/>
       <c r="U20" s="41"/>
@@ -4744,10 +4747,10 @@
         <v>162</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="T21" s="41"/>
       <c r="U21" s="41"/>
@@ -4789,13 +4792,13 @@
         <v>335</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="T22" s="41"/>
       <c r="U22" s="41"/>
@@ -4831,7 +4834,7 @@
         <v>273</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="T23" s="41"/>
       <c r="U23" s="41"/>
@@ -4840,18 +4843,18 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>931</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>932</v>
-      </c>
       <c r="D24" s="13" t="s">
-        <v>977</v>
-      </c>
-      <c r="E24" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>274</v>
       </c>
       <c r="T24" s="41"/>
@@ -4897,30 +4900,30 @@
         <v>169</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>274</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="S25" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="T25" s="47" t="s">
         <v>1002</v>
       </c>
-      <c r="T25" s="47" t="s">
-        <v>1003</v>
-      </c>
-      <c r="U25" s="41" t="s">
+      <c r="U25" s="44" t="s">
         <v>432</v>
       </c>
       <c r="V25" s="41"/>
@@ -4946,16 +4949,16 @@
         <v>278</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>897</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>1054</v>
+      <c r="J26" s="6" t="s">
+        <v>1053</v>
       </c>
       <c r="T26" s="41"/>
       <c r="U26" s="41"/>
@@ -4994,7 +4997,7 @@
         <v>326</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="T27" s="41"/>
       <c r="U27" s="41"/>
@@ -5033,13 +5036,13 @@
         <v>430</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>956</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>1050</v>
+        <v>955</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>1049</v>
       </c>
       <c r="T28" s="41"/>
       <c r="U28" s="41"/>
@@ -5083,8 +5086,8 @@
       <c r="L29" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>1037</v>
+      <c r="M29" s="11" t="s">
+        <v>1036</v>
       </c>
       <c r="T29" s="41"/>
       <c r="U29" s="41"/>
@@ -5126,21 +5129,21 @@
         <v>197</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>173</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>1023</v>
-      </c>
-      <c r="Q30" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Q30" s="6" t="s">
         <v>312</v>
       </c>
       <c r="T30" s="41"/>
@@ -5177,25 +5180,25 @@
         <v>307</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>432</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>429</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="T31" s="41"/>
       <c r="U31" s="41"/>
@@ -5240,15 +5243,15 @@
         <v>335</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>1024</v>
-      </c>
-      <c r="P32" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="P32" s="11" t="s">
         <v>162</v>
       </c>
       <c r="T32" s="41"/>
@@ -5294,7 +5297,7 @@
         <v>322</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="T33" s="41"/>
       <c r="U33" s="41"/>
@@ -5330,19 +5333,19 @@
         <v>272</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>170</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="T34" s="41"/>
       <c r="U34" s="41"/>
@@ -5381,7 +5384,7 @@
         <v>276</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="T35" s="41"/>
       <c r="U35" s="41"/>
@@ -5414,7 +5417,7 @@
         <v>171</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J36" s="10" t="s">
         <v>265</v>
@@ -5429,13 +5432,13 @@
         <v>173</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>232</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="T36" s="41"/>
       <c r="U36" s="41"/>
@@ -5492,25 +5495,25 @@
         <v>339</v>
       </c>
       <c r="Q37" s="10" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="S37" s="40" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="T37" s="43" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="U37" s="44" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="V37" s="49" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="W37" s="50" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
@@ -5548,13 +5551,13 @@
         <v>347</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>1042</v>
+      <c r="N38" s="8" t="s">
+        <v>1041</v>
       </c>
       <c r="T38" s="41"/>
       <c r="U38" s="41"/>
@@ -5599,21 +5602,21 @@
         <v>197</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="N39" s="10" t="s">
         <v>326</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="R39" s="1" t="s">
+      <c r="R39" s="6" t="s">
         <v>162</v>
       </c>
       <c r="T39" s="41"/>
@@ -5653,7 +5656,7 @@
         <v>359</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>360</v>
@@ -5662,7 +5665,7 @@
         <v>240</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="T40" s="41"/>
       <c r="U40" s="41"/>
@@ -5701,10 +5704,10 @@
         <v>365</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>900</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>1052</v>
+        <v>899</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>1051</v>
       </c>
       <c r="T41" s="41"/>
       <c r="U41" s="41"/>
@@ -5749,7 +5752,7 @@
         <v>373</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N42" s="13" t="s">
         <v>183</v>
@@ -5800,19 +5803,19 @@
         <v>312</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>274</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="Q43" s="10" t="s">
-        <v>986</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>1040</v>
+        <v>985</v>
+      </c>
+      <c r="R43" s="9" t="s">
+        <v>1039</v>
       </c>
       <c r="T43" s="41"/>
       <c r="U43" s="41"/>
@@ -5836,7 +5839,7 @@
         <v>239</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>222</v>
@@ -5851,10 +5854,10 @@
         <v>172</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>933</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>982</v>
+        <v>932</v>
+      </c>
+      <c r="L44" s="12" t="s">
+        <v>981</v>
       </c>
       <c r="T44" s="41"/>
       <c r="U44" s="41"/>
@@ -5908,7 +5911,7 @@
         <v>232</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="T45" s="41"/>
       <c r="U45" s="41"/>
@@ -5953,13 +5956,13 @@
         <v>393</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="T46" s="41"/>
       <c r="U46" s="41"/>
@@ -5977,16 +5980,16 @@
         <v>252</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>972</v>
+      <c r="G47" s="13" t="s">
+        <v>971</v>
       </c>
       <c r="T47" s="41"/>
       <c r="U47" s="41"/>
@@ -6031,9 +6034,9 @@
         <v>278</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="N48" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="N48" s="6" t="s">
         <v>224</v>
       </c>
       <c r="T48" s="41"/>
@@ -6070,10 +6073,10 @@
         <v>273</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="T49" s="41"/>
       <c r="U49" s="41"/>
@@ -6082,15 +6085,15 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>897</v>
-      </c>
-      <c r="D50" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>173</v>
       </c>
       <c r="T50" s="41"/>
@@ -6115,10 +6118,10 @@
         <v>405</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="T51" s="41"/>
       <c r="U51" s="41"/>
@@ -6157,19 +6160,19 @@
         <v>183</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="L52" s="10" t="s">
         <v>232</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="O52" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>173</v>
@@ -6193,7 +6196,7 @@
         <v>301</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>240</v>
@@ -6250,13 +6253,13 @@
         <v>675</v>
       </c>
       <c r="O54" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="P54" s="8" t="s">
         <v>884</v>
       </c>
-      <c r="P54" s="8" t="s">
-        <v>885</v>
-      </c>
       <c r="Q54" s="6" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="T54" s="41"/>
       <c r="U54" s="41"/>
@@ -6304,16 +6307,16 @@
         <v>197</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="O55" s="8" t="s">
         <v>224</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>1039</v>
+        <v>899</v>
+      </c>
+      <c r="Q55" s="8" t="s">
+        <v>1038</v>
       </c>
       <c r="T55" s="41"/>
       <c r="U55" s="41"/>
@@ -6364,10 +6367,10 @@
         <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="Q56" s="11" t="s">
         <v>658</v>
@@ -6406,22 +6409,22 @@
         <v>266</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K57" s="10" t="s">
+        <v>981</v>
+      </c>
+      <c r="L57" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="L57" s="8" t="s">
-        <v>983</v>
-      </c>
       <c r="M57" s="6" t="s">
-        <v>1004</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>1054</v>
+        <v>1003</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>1053</v>
       </c>
       <c r="T57" s="41"/>
       <c r="U57" s="41"/>
@@ -6457,18 +6460,18 @@
         <v>431</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="N58" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="N58" s="8" t="s">
         <v>278</v>
       </c>
       <c r="T58" s="41"/>
@@ -6508,22 +6511,22 @@
         <v>230</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="P59" s="11" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="T59" s="41"/>
       <c r="U59" s="41"/>
@@ -6544,7 +6547,7 @@
         <v>171</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>277</v>
@@ -6556,28 +6559,28 @@
         <v>175</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="K60" s="8" t="s">
         <v>170</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="N60" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="O60" s="1" t="s">
+      <c r="O60" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="P60" s="8" t="s">
         <v>970</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>971</v>
       </c>
       <c r="T60" s="41"/>
       <c r="U60" s="41"/>
@@ -6595,7 +6598,7 @@
         <v>161</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>192</v>
@@ -6604,9 +6607,9 @@
         <v>191</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="H61" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>440</v>
       </c>
       <c r="T61" s="41"/>
@@ -6655,15 +6658,15 @@
         <v>313</v>
       </c>
       <c r="N62" s="8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="P62" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="Q62" s="1" t="s">
+      <c r="Q62" s="6" t="s">
         <v>173</v>
       </c>
       <c r="T62" s="41"/>
@@ -6700,12 +6703,12 @@
         <v>177</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K63" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="L63" s="6" t="s">
         <v>278</v>
       </c>
       <c r="T63" s="41"/>
@@ -6745,7 +6748,7 @@
         <v>774</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="T64" s="41"/>
       <c r="U64" s="41"/>
@@ -6802,19 +6805,19 @@
         <v>232</v>
       </c>
       <c r="Q65" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="R65" s="7" t="s">
         <v>908</v>
       </c>
-      <c r="R65" s="7" t="s">
-        <v>909</v>
-      </c>
       <c r="S65" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="T65" s="48" t="s">
-        <v>1017</v>
-      </c>
-      <c r="U65" s="41" t="s">
-        <v>1054</v>
+        <v>1016</v>
+      </c>
+      <c r="U65" s="48" t="s">
+        <v>1053</v>
       </c>
       <c r="V65" s="41"/>
       <c r="W65" s="2"/>
@@ -6860,21 +6863,21 @@
         <v>260</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P66" s="8" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="Q66" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="R66" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="R66" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="S66" s="1" t="s">
+      <c r="S66" s="7" t="s">
         <v>173</v>
       </c>
       <c r="T66" s="41"/>
@@ -6899,13 +6902,13 @@
         <v>224</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>274</v>
@@ -6977,7 +6980,7 @@
         <v>289</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>163</v>
@@ -6986,7 +6989,7 @@
         <v>556</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="T69" s="41"/>
       <c r="U69" s="41"/>
@@ -7010,19 +7013,19 @@
         <v>173</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="T70" s="41"/>
       <c r="U70" s="41"/>
@@ -7046,7 +7049,7 @@
         <v>191</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="T71" s="41"/>
       <c r="U71" s="41"/>
@@ -7097,7 +7100,7 @@
         <v>484</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="P72" s="11" t="s">
         <v>430</v>
@@ -7113,19 +7116,19 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>894</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C73" s="10" t="s">
+      <c r="D73" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>896</v>
-      </c>
       <c r="E73" s="11" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="T73" s="41"/>
       <c r="U73" s="41"/>
@@ -7164,10 +7167,10 @@
         <v>276</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>335</v>
@@ -7176,7 +7179,7 @@
         <v>326</v>
       </c>
       <c r="O74" s="8" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="T74" s="41"/>
       <c r="U74" s="41"/>
@@ -7221,7 +7224,7 @@
         <v>224</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N75" s="11" t="s">
         <v>373</v>
@@ -7230,19 +7233,19 @@
         <v>235</v>
       </c>
       <c r="P75" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="Q75" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="R75" s="11" t="s">
         <v>949</v>
       </c>
-      <c r="R75" s="11" t="s">
-        <v>950</v>
-      </c>
       <c r="S75" s="10" t="s">
-        <v>982</v>
-      </c>
-      <c r="T75" s="41" t="s">
-        <v>917</v>
+        <v>981</v>
+      </c>
+      <c r="T75" s="43" t="s">
+        <v>916</v>
       </c>
       <c r="U75" s="41"/>
       <c r="V75" s="41"/>
@@ -7289,7 +7292,7 @@
         <v>431</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>335</v>
@@ -7298,13 +7301,13 @@
         <v>232</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T76" s="41"/>
       <c r="U76" s="41"/>
@@ -7328,13 +7331,13 @@
         <v>430</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>1054</v>
+        <v>907</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>1053</v>
       </c>
       <c r="T77" s="41"/>
       <c r="U77" s="41"/>
@@ -7364,16 +7367,16 @@
         <v>429</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I78" s="12" t="s">
         <v>252</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>1042</v>
+        <v>860</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>1041</v>
       </c>
       <c r="T78" s="41"/>
       <c r="U78" s="41"/>
@@ -7409,7 +7412,7 @@
         <v>272</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>162</v>
@@ -7418,16 +7421,16 @@
         <v>278</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="O79" s="11" t="s">
-        <v>1021</v>
-      </c>
-      <c r="P79" s="1" t="s">
-        <v>1048</v>
+        <v>1020</v>
+      </c>
+      <c r="P79" s="7" t="s">
+        <v>1047</v>
       </c>
       <c r="T79" s="41"/>
       <c r="U79" s="41"/>
@@ -7469,15 +7472,15 @@
         <v>252</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M80" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="O80" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="O80" s="9" t="s">
         <v>278</v>
       </c>
       <c r="T80" s="41"/>
@@ -7523,7 +7526,7 @@
         <v>274</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N81" s="6" t="s">
         <v>429</v>
@@ -7535,25 +7538,25 @@
         <v>252</v>
       </c>
       <c r="Q81" s="8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="R81" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="S81" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="T81" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="U81" s="47" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="V81" s="48" t="s">
-        <v>871</v>
-      </c>
-      <c r="W81" s="2" t="s">
-        <v>1045</v>
+        <v>870</v>
+      </c>
+      <c r="W81" s="55" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
@@ -7591,13 +7594,13 @@
         <v>289</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>373</v>
       </c>
       <c r="N82" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>556</v>
@@ -7648,13 +7651,13 @@
         <v>335</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="T83" s="41"/>
       <c r="U83" s="41"/>
@@ -7696,7 +7699,7 @@
         <v>240</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="T84" s="41"/>
       <c r="U84" s="41"/>
@@ -7750,13 +7753,13 @@
         <v>173</v>
       </c>
       <c r="P85" s="13" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="Q85" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="R85" s="10" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="T85" s="41"/>
       <c r="U85" s="41"/>
@@ -7765,16 +7768,16 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D86" s="45" t="s">
-        <v>898</v>
+      <c r="D86" s="7" t="s">
+        <v>897</v>
       </c>
       <c r="E86" s="45"/>
       <c r="F86" s="45"/>
@@ -7796,18 +7799,18 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>972</v>
-      </c>
-      <c r="E87" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="E87" s="6" t="s">
         <v>439</v>
       </c>
       <c r="T87" s="41"/>
@@ -7862,7 +7865,7 @@
         <v>326</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="Q88" s="8" t="s">
         <v>313</v>
@@ -7871,16 +7874,16 @@
         <v>609</v>
       </c>
       <c r="S88" s="11" t="s">
+        <v>904</v>
+      </c>
+      <c r="T88" s="44" t="s">
         <v>905</v>
       </c>
-      <c r="T88" s="44" t="s">
-        <v>906</v>
-      </c>
       <c r="U88" s="44" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V88" s="44" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="W88" s="51" t="s">
         <v>307</v>
@@ -7915,19 +7918,19 @@
         <v>183</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>232</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="T89" s="41"/>
       <c r="U89" s="41"/>
@@ -7975,22 +7978,22 @@
         <v>440</v>
       </c>
       <c r="N90" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O90" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="P90" s="7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="R90" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="R90" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="S90" s="1" t="s">
-        <v>1049</v>
+      <c r="S90" s="6" t="s">
+        <v>1048</v>
       </c>
       <c r="T90" s="41"/>
       <c r="U90" s="41"/>
@@ -7999,19 +8002,19 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>183</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="T91" s="41"/>
       <c r="U91" s="41"/>
@@ -8056,16 +8059,16 @@
         <v>252</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N92" s="8" t="s">
         <v>276</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="P92" s="1" t="s">
-        <v>1048</v>
+        <v>899</v>
+      </c>
+      <c r="P92" s="8" t="s">
+        <v>1047</v>
       </c>
       <c r="T92" s="41"/>
       <c r="U92" s="41"/>
@@ -8110,13 +8113,13 @@
         <v>252</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N93" s="8" t="s">
         <v>224</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="T93" s="41"/>
       <c r="U93" s="41"/>
@@ -8137,7 +8140,7 @@
         <v>558</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>388</v>
@@ -8152,16 +8155,16 @@
         <v>430</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>952</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>1050</v>
+        <v>951</v>
+      </c>
+      <c r="M94" s="8" t="s">
+        <v>1049</v>
       </c>
       <c r="T94" s="41"/>
       <c r="U94" s="41"/>
@@ -8182,7 +8185,7 @@
         <v>170</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>430</v>
@@ -8191,13 +8194,13 @@
         <v>326</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>992</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>1043</v>
+        <v>991</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>1042</v>
       </c>
       <c r="T95" s="41"/>
       <c r="U95" s="41"/>
@@ -8248,15 +8251,15 @@
         <v>431</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="P96" s="13" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="Q96" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="R96" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="R96" s="6" t="s">
         <v>173</v>
       </c>
       <c r="T96" s="41"/>
@@ -8266,7 +8269,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>157</v>
@@ -8277,8 +8280,8 @@
       <c r="D97" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>917</v>
+      <c r="E97" s="8" t="s">
+        <v>916</v>
       </c>
       <c r="T97" s="41"/>
       <c r="U97" s="41"/>
@@ -8311,16 +8314,16 @@
         <v>566</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="J98" s="6" t="s">
         <v>194</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L98" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="T98" s="41"/>
       <c r="U98" s="41"/>
@@ -8362,13 +8365,13 @@
         <v>252</v>
       </c>
       <c r="L99" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="T99" s="41"/>
       <c r="U99" s="41"/>
@@ -8407,10 +8410,10 @@
         <v>260</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L100" s="13" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M100" s="10" t="s">
         <v>177</v>
@@ -8455,13 +8458,13 @@
         <v>273</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="M101" s="8" t="s">
         <v>170</v>
       </c>
       <c r="N101" s="7" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="T101" s="41"/>
       <c r="U101" s="41"/>
@@ -8485,10 +8488,10 @@
         <v>252</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>955</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>1052</v>
+        <v>954</v>
+      </c>
+      <c r="G102" s="11" t="s">
+        <v>1051</v>
       </c>
       <c r="T102" s="41"/>
       <c r="U102" s="41"/>
@@ -8533,13 +8536,13 @@
         <v>313</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="T103" s="41"/>
       <c r="U103" s="41"/>
@@ -8587,9 +8590,9 @@
         <v>326</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>821</v>
-      </c>
-      <c r="O104" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="O104" s="10" t="s">
         <v>432</v>
       </c>
       <c r="T104" s="41"/>
@@ -8617,28 +8620,28 @@
         <v>339</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L105" s="11" t="s">
-        <v>891</v>
-      </c>
-      <c r="M105" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="N105" s="1" t="s">
-        <v>982</v>
+        <v>890</v>
+      </c>
+      <c r="M105" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="N105" s="11" t="s">
+        <v>981</v>
       </c>
       <c r="T105" s="41"/>
       <c r="U105" s="41"/>
@@ -8659,7 +8662,7 @@
         <v>184</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F106" s="13" t="s">
         <v>307</v>
@@ -8671,10 +8674,10 @@
         <v>509</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="T106" s="41"/>
       <c r="U106" s="41"/>
@@ -8740,16 +8743,16 @@
         <v>278</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="L108" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="M108" s="10" t="s">
         <v>944</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>945</v>
       </c>
       <c r="N108" s="11" t="s">
         <v>274</v>
@@ -8797,7 +8800,7 @@
         <v>240</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="T109" s="41"/>
       <c r="U109" s="41"/>
@@ -8824,7 +8827,7 @@
         <v>172</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="T110" s="41"/>
       <c r="U110" s="41"/>
@@ -8848,7 +8851,7 @@
         <v>232</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="T111" s="41"/>
       <c r="U111" s="41"/>
@@ -8857,25 +8860,25 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>840</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>841</v>
-      </c>
       <c r="D112" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E112" s="7" t="s">
+        <v>932</v>
+      </c>
+      <c r="F112" s="10" t="s">
         <v>933</v>
       </c>
-      <c r="F112" s="10" t="s">
-        <v>934</v>
-      </c>
       <c r="G112" s="6" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="T112" s="41"/>
       <c r="U112" s="41"/>
@@ -8929,10 +8932,10 @@
         <v>440</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="Q113" s="1" t="s">
-        <v>917</v>
+        <v>934</v>
+      </c>
+      <c r="Q113" s="11" t="s">
+        <v>916</v>
       </c>
       <c r="T113" s="41"/>
       <c r="U113" s="41"/>
@@ -8965,10 +8968,10 @@
         <v>417</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="T114" s="41"/>
       <c r="U114" s="41"/>
@@ -8992,7 +8995,7 @@
         <v>609</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G115" s="11" t="s">
         <v>610</v>
@@ -9001,7 +9004,7 @@
         <v>169</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>440</v>
@@ -9013,22 +9016,22 @@
         <v>611</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>173</v>
       </c>
       <c r="O115" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P115" s="11" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="R115" s="8" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="T115" s="41"/>
       <c r="U115" s="41"/>
@@ -9058,7 +9061,7 @@
         <v>252</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="T116" s="41"/>
       <c r="U116" s="41"/>
@@ -9103,7 +9106,7 @@
         <v>192</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="N117" s="11" t="s">
         <v>417</v>
@@ -9111,7 +9114,7 @@
       <c r="O117" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="P117" s="1" t="s">
+      <c r="P117" s="6" t="s">
         <v>161</v>
       </c>
       <c r="T117" s="41"/>
@@ -9136,12 +9139,12 @@
         <v>232</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>1016</v>
-      </c>
-      <c r="H118" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H118" s="10" t="s">
         <v>393</v>
       </c>
       <c r="T118" s="41"/>
@@ -9208,7 +9211,7 @@
         <v>184</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>232</v>
@@ -9220,7 +9223,7 @@
         <v>500</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I120" s="6" t="s">
         <v>326</v>
@@ -9229,10 +9232,10 @@
         <v>170</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="T120" s="41"/>
       <c r="U120" s="41"/>
@@ -9247,33 +9250,33 @@
         <v>157</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>797</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>798</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="E121" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>800</v>
-      </c>
       <c r="F121" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="H121" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="H121" s="8" t="s">
-        <v>878</v>
-      </c>
       <c r="I121" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>170</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="L121" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="L121" s="6" t="s">
         <v>432</v>
       </c>
       <c r="T121" s="41"/>
@@ -9295,7 +9298,7 @@
         <v>628</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>273</v>
@@ -9307,16 +9310,16 @@
         <v>173</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K122" s="8" t="s">
-        <v>1015</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>1034</v>
+        <v>1014</v>
+      </c>
+      <c r="L122" s="9" t="s">
+        <v>1033</v>
       </c>
       <c r="T122" s="41"/>
       <c r="U122" s="41"/>
@@ -9358,22 +9361,22 @@
         <v>483</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M123" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N123" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="O123" s="13" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="Q123" s="12" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="T123" s="41"/>
       <c r="U123" s="41"/>
@@ -9418,10 +9421,10 @@
         <v>774</v>
       </c>
       <c r="M124" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="T124" s="41"/>
       <c r="U124" s="41"/>
@@ -9448,7 +9451,7 @@
         <v>642</v>
       </c>
       <c r="G125" s="11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H125" s="13" t="s">
         <v>222</v>
@@ -9457,7 +9460,7 @@
         <v>313</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="T125" s="41"/>
       <c r="U125" s="41"/>
@@ -9505,7 +9508,7 @@
         <v>240</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="T126" s="41"/>
       <c r="U126" s="41"/>
@@ -9544,10 +9547,10 @@
         <v>232</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="T127" s="41"/>
       <c r="U127" s="41"/>
@@ -9598,22 +9601,22 @@
         <v>163</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>499</v>
       </c>
       <c r="Q128" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="R128" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="R128" s="7" t="s">
-        <v>901</v>
-      </c>
       <c r="S128" s="9" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="T128" s="47" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="U128" s="41"/>
       <c r="V128" s="41"/>
@@ -9641,7 +9644,7 @@
       <c r="G129" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" s="13" t="s">
         <v>312</v>
       </c>
       <c r="T129" s="41"/>
@@ -9651,15 +9654,15 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="9" t="s">
         <v>948</v>
       </c>
-      <c r="B130" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>949</v>
-      </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="13" t="s">
         <v>478</v>
       </c>
       <c r="T130" s="41"/>
@@ -9702,22 +9705,22 @@
         <v>339</v>
       </c>
       <c r="L131" s="13" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M131" s="9" t="s">
         <v>170</v>
       </c>
       <c r="N131" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="O131" s="7" t="s">
         <v>925</v>
-      </c>
-      <c r="O131" s="7" t="s">
-        <v>926</v>
       </c>
       <c r="P131" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="Q131" s="1" t="s">
-        <v>1034</v>
+      <c r="Q131" s="9" t="s">
+        <v>1033</v>
       </c>
       <c r="T131" s="41"/>
       <c r="U131" s="41"/>
@@ -9765,22 +9768,22 @@
         <v>224</v>
       </c>
       <c r="N132" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="P132" s="9" t="s">
         <v>173</v>
       </c>
       <c r="Q132" s="6" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="R132" s="8" t="s">
-        <v>908</v>
-      </c>
-      <c r="S132" s="1" t="s">
-        <v>1042</v>
+        <v>907</v>
+      </c>
+      <c r="S132" s="8" t="s">
+        <v>1041</v>
       </c>
       <c r="T132" s="41"/>
       <c r="U132" s="41"/>
@@ -9813,13 +9816,13 @@
         <v>675</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J133" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="K133" s="8" t="s">
         <v>998</v>
-      </c>
-      <c r="K133" s="8" t="s">
-        <v>999</v>
       </c>
       <c r="T133" s="41"/>
       <c r="U133" s="41"/>
@@ -9843,22 +9846,22 @@
         <v>183</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J134" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="K134" s="1" t="s">
-        <v>983</v>
+      <c r="K134" s="9" t="s">
+        <v>982</v>
       </c>
       <c r="T134" s="41"/>
       <c r="U134" s="41"/>
@@ -9900,7 +9903,7 @@
         <v>326</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M135" s="9" t="s">
         <v>173</v>
@@ -9909,7 +9912,7 @@
         <v>276</v>
       </c>
       <c r="O135" s="6" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="T135" s="41"/>
       <c r="U135" s="41"/>
@@ -9966,10 +9969,10 @@
         <v>170</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>921</v>
-      </c>
-      <c r="H137" s="1" t="s">
-        <v>1051</v>
+        <v>920</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>1050</v>
       </c>
       <c r="T137" s="41"/>
       <c r="U137" s="41"/>
@@ -10011,13 +10014,13 @@
         <v>232</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="N138" s="8" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="T138" s="41"/>
       <c r="U138" s="41"/>
@@ -10050,7 +10053,7 @@
         <v>252</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="T139" s="41"/>
       <c r="U139" s="41"/>
@@ -10098,7 +10101,7 @@
         <v>173</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="O140" s="10" t="s">
         <v>432</v>
@@ -10106,8 +10109,8 @@
       <c r="P140" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="Q140" s="1" t="s">
-        <v>1034</v>
+      <c r="Q140" s="6" t="s">
+        <v>1033</v>
       </c>
       <c r="T140" s="41"/>
       <c r="U140" s="41"/>
@@ -10125,7 +10128,7 @@
         <v>691</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>161</v>
@@ -10143,7 +10146,7 @@
         <v>272</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K141" s="11" t="s">
         <v>373</v>
@@ -10152,19 +10155,19 @@
         <v>173</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N141" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O141" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="T141" s="41"/>
       <c r="U141" s="41"/>
@@ -10221,10 +10224,10 @@
         <v>173</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>908</v>
-      </c>
-      <c r="R142" s="1" t="s">
-        <v>972</v>
+        <v>907</v>
+      </c>
+      <c r="R142" s="10" t="s">
+        <v>971</v>
       </c>
       <c r="T142" s="41"/>
       <c r="U142" s="41"/>
@@ -10257,10 +10260,10 @@
         <v>260</v>
       </c>
       <c r="I143" s="9" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="T143" s="41"/>
       <c r="U143" s="41"/>
@@ -10310,8 +10313,8 @@
       <c r="N144" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="O144" s="1" t="s">
-        <v>1040</v>
+      <c r="O144" s="9" t="s">
+        <v>1039</v>
       </c>
       <c r="T144" s="41"/>
       <c r="U144" s="41"/>
@@ -10332,7 +10335,7 @@
         <v>707</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>328</v>
@@ -10365,7 +10368,7 @@
         <v>431</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="Q145" s="12" t="s">
         <v>252</v>
@@ -10422,7 +10425,7 @@
         <v>232</v>
       </c>
       <c r="O146" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="P146" s="13" t="s">
         <v>273</v>
@@ -10455,7 +10458,7 @@
         <v>720</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="T147" s="41"/>
       <c r="U147" s="41"/>
@@ -10470,7 +10473,7 @@
         <v>157</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>573</v>
@@ -10485,10 +10488,10 @@
         <v>721</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="T148" s="41"/>
       <c r="U148" s="41"/>
@@ -10536,16 +10539,16 @@
         <v>232</v>
       </c>
       <c r="N149" s="6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O149" s="8" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="Q149" s="1" t="s">
-        <v>982</v>
+      <c r="Q149" s="6" t="s">
+        <v>981</v>
       </c>
       <c r="T149" s="41"/>
       <c r="U149" s="41"/>
@@ -10587,7 +10590,7 @@
         <v>432</v>
       </c>
       <c r="L150" s="10" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M150" s="10" t="s">
         <v>173</v>
@@ -10596,19 +10599,19 @@
         <v>373</v>
       </c>
       <c r="O150" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P150" s="12" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="Q150" s="8" t="s">
         <v>440</v>
       </c>
       <c r="R150" s="8" t="s">
-        <v>944</v>
-      </c>
-      <c r="S150" s="1" t="s">
-        <v>970</v>
+        <v>943</v>
+      </c>
+      <c r="S150" s="6" t="s">
+        <v>969</v>
       </c>
       <c r="T150" s="41"/>
       <c r="U150" s="41"/>
@@ -10659,13 +10662,13 @@
         <v>240</v>
       </c>
       <c r="O151" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="P151" s="13" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="Q151" s="8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="T151" s="41"/>
       <c r="U151" s="41"/>
@@ -10695,7 +10698,7 @@
         <v>196</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="T152" s="41"/>
       <c r="U152" s="41"/>
@@ -10704,7 +10707,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>157</v>
@@ -10713,10 +10716,10 @@
         <v>440</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>1032</v>
+        <v>894</v>
+      </c>
+      <c r="E153" s="10" t="s">
+        <v>1031</v>
       </c>
       <c r="T153" s="41"/>
       <c r="U153" s="41"/>
@@ -10755,19 +10758,19 @@
         <v>339</v>
       </c>
       <c r="K154" s="9" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L154" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>982</v>
+        <v>999</v>
+      </c>
+      <c r="O154" s="10" t="s">
+        <v>981</v>
       </c>
       <c r="T154" s="41"/>
       <c r="U154" s="41"/>
@@ -10785,22 +10788,22 @@
         <v>197</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>595</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>990</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>1053</v>
+        <v>989</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>1052</v>
       </c>
       <c r="T155" s="41"/>
       <c r="U155" s="41"/>
@@ -10833,10 +10836,10 @@
         <v>232</v>
       </c>
       <c r="I156" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J156" s="1" t="s">
-        <v>1046</v>
+        <v>1006</v>
+      </c>
+      <c r="J156" s="8" t="s">
+        <v>1045</v>
       </c>
       <c r="T156" s="41"/>
       <c r="U156" s="41"/>
@@ -10881,13 +10884,13 @@
         <v>746</v>
       </c>
       <c r="M157" s="11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="T157" s="41"/>
       <c r="U157" s="41"/>
@@ -10920,16 +10923,16 @@
         <v>750</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="L158" s="1" t="s">
-        <v>1034</v>
+        <v>916</v>
+      </c>
+      <c r="L158" s="13" t="s">
+        <v>1033</v>
       </c>
       <c r="T158" s="41"/>
       <c r="U158" s="41"/>
@@ -10977,16 +10980,16 @@
         <v>183</v>
       </c>
       <c r="N159" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="O159" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="P159" s="6" t="s">
         <v>897</v>
       </c>
-      <c r="P159" s="6" t="s">
-        <v>898</v>
-      </c>
       <c r="Q159" s="6" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="T159" s="41"/>
       <c r="U159" s="41"/>
@@ -11024,7 +11027,7 @@
       <c r="J160" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="K160" s="1" t="s">
+      <c r="K160" s="9" t="s">
         <v>312</v>
       </c>
       <c r="T160" s="41"/>
@@ -11055,22 +11058,22 @@
         <v>172</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="J161" s="8" t="s">
         <v>278</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N161" s="8" t="s">
         <v>274</v>
@@ -11109,7 +11112,7 @@
         <v>240</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="T162" s="41"/>
       <c r="U162" s="41"/>
@@ -11120,19 +11123,19 @@
       <c r="A163" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B163" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C163" s="45" t="s">
+      <c r="B163" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C163" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="D163" s="45" t="s">
+      <c r="D163" s="9" t="s">
         <v>507</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>766</v>
       </c>
-      <c r="F163" s="45" t="s">
+      <c r="F163" s="10" t="s">
         <v>767</v>
       </c>
       <c r="G163" s="6" t="s">
@@ -11153,8 +11156,8 @@
       <c r="L163" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="M163" s="1" t="s">
-        <v>1041</v>
+      <c r="M163" s="8" t="s">
+        <v>1040</v>
       </c>
       <c r="T163" s="41"/>
       <c r="U163" s="41"/>
@@ -11190,37 +11193,37 @@
         <v>184</v>
       </c>
       <c r="J164" s="10" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K164" s="7" t="s">
         <v>173</v>
       </c>
       <c r="L164" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="M164" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="M164" s="5" t="s">
-        <v>815</v>
-      </c>
       <c r="N164" s="6" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="P164" s="10" t="s">
         <v>917</v>
       </c>
-      <c r="P164" s="10" t="s">
-        <v>918</v>
-      </c>
       <c r="Q164" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="R164" s="11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="S164" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="T164" s="41" t="s">
-        <v>1054</v>
+        <v>993</v>
+      </c>
+      <c r="T164" s="44" t="s">
+        <v>1053</v>
       </c>
       <c r="U164" s="41"/>
       <c r="V164" s="41"/>
@@ -11243,28 +11246,28 @@
         <v>440</v>
       </c>
       <c r="F165" s="13" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H165" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="I165" s="9" t="s">
         <v>937</v>
-      </c>
-      <c r="I165" s="9" t="s">
-        <v>938</v>
       </c>
       <c r="J165" s="6" t="s">
         <v>232</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>1021</v>
-      </c>
-      <c r="M165" s="1" t="s">
-        <v>982</v>
+        <v>1020</v>
+      </c>
+      <c r="M165" s="6" t="s">
+        <v>981</v>
       </c>
       <c r="T165" s="41"/>
       <c r="U165" s="41"/>
@@ -11294,7 +11297,7 @@
         <v>266</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I166" s="10" t="s">
         <v>173</v>
@@ -11302,7 +11305,7 @@
       <c r="J166" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="K166" s="1" t="s">
+      <c r="K166" s="11" t="s">
         <v>232</v>
       </c>
       <c r="T166" s="41"/>
@@ -11312,13 +11315,13 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C167" s="10" t="s">
         <v>1033</v>
-      </c>
-      <c r="B167" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C167" s="45" t="s">
-        <v>1034</v>
       </c>
       <c r="D167" s="45"/>
       <c r="E167" s="45"/>
@@ -11352,21 +11355,21 @@
         <v>326</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="I168" s="11" t="s">
+        <v>972</v>
+      </c>
+      <c r="J168" s="10" t="s">
         <v>973</v>
       </c>
-      <c r="J168" s="10" t="s">
-        <v>974</v>
-      </c>
-      <c r="K168" s="1" t="s">
+      <c r="K168" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="L168" s="1" t="s">
+      <c r="L168" s="9" t="s">
         <v>432</v>
       </c>
       <c r="T168" s="41"/>
@@ -11376,13 +11379,13 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B169" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C169" s="45" t="s">
-        <v>925</v>
+        <v>1046</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>924</v>
       </c>
       <c r="D169" s="45"/>
       <c r="E169" s="45"/>
@@ -11416,10 +11419,10 @@
         <v>481</v>
       </c>
       <c r="G170" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="T170" s="41"/>
       <c r="U170" s="41"/>
@@ -11443,7 +11446,7 @@
         <v>183</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G171" s="10" t="s">
         <v>458</v>
@@ -11455,25 +11458,25 @@
         <v>339</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>335</v>
       </c>
       <c r="L171" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M171" s="8" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="N171" s="10" t="s">
         <v>161</v>
       </c>
       <c r="O171" s="6" t="s">
-        <v>1022</v>
-      </c>
-      <c r="P171" s="1" t="s">
-        <v>871</v>
+        <v>1021</v>
+      </c>
+      <c r="P171" s="10" t="s">
+        <v>870</v>
       </c>
       <c r="T171" s="41"/>
       <c r="U171" s="41"/>
@@ -11482,7 +11485,7 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>157</v>
@@ -11491,18 +11494,18 @@
         <v>677</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>989</v>
-      </c>
-      <c r="H172" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="H172" s="9" t="s">
         <v>439</v>
       </c>
       <c r="T172" s="41"/>
@@ -11545,12 +11548,12 @@
         <v>194</v>
       </c>
       <c r="L173" s="11" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M173" s="12" t="s">
-        <v>933</v>
-      </c>
-      <c r="N173" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="N173" s="13" t="s">
         <v>432</v>
       </c>
       <c r="T173" s="41"/>
@@ -11584,9 +11587,9 @@
         <v>265</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>897</v>
-      </c>
-      <c r="J174" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="J174" s="8" t="s">
         <v>278</v>
       </c>
       <c r="T174" s="41"/>
@@ -11614,19 +11617,19 @@
         <v>483</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I175" s="10" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="J175" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="K175" s="1" t="s">
-        <v>1044</v>
+      <c r="K175" s="6" t="s">
+        <v>1043</v>
       </c>
       <c r="T175" s="41"/>
       <c r="U175" s="41"/>
@@ -11656,19 +11659,19 @@
         <v>276</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I176" s="36" t="s">
         <v>675</v>
       </c>
       <c r="J176" s="18" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K176" s="18" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="M176" s="52" t="s">
         <v>161</v>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="1056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="1058">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3192,6 +3192,12 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Prestige Requiem</t>
+  </si>
+  <si>
+    <t>Corrupted Petricite</t>
   </si>
 </sst>
 </file>
@@ -3577,13 +3583,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3982,24 +3988,24 @@
       <c r="A4" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
       <c r="R4" s="38"/>
       <c r="S4" s="3"/>
       <c r="T4" s="37"/>
@@ -7555,7 +7561,7 @@
       <c r="V81" s="48" t="s">
         <v>870</v>
       </c>
-      <c r="W81" s="55" t="s">
+      <c r="W81" s="53" t="s">
         <v>1044</v>
       </c>
     </row>
@@ -7700,6 +7706,9 @@
       </c>
       <c r="L84" s="11" t="s">
         <v>918</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="T84" s="41"/>
       <c r="U84" s="41"/>
@@ -9722,6 +9731,9 @@
       <c r="Q131" s="9" t="s">
         <v>1033</v>
       </c>
+      <c r="R131" s="1" t="s">
+        <v>1056</v>
+      </c>
       <c r="T131" s="41"/>
       <c r="U131" s="41"/>
       <c r="V131" s="41"/>
@@ -11113,6 +11125,9 @@
       </c>
       <c r="J162" s="6" t="s">
         <v>951</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="T162" s="41"/>
       <c r="U162" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="1059">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3198,6 +3198,9 @@
   </si>
   <si>
     <t>Corrupted Petricite</t>
+  </si>
+  <si>
+    <t>Warhound</t>
   </si>
 </sst>
 </file>
@@ -8025,6 +8028,9 @@
       <c r="E91" s="13" t="s">
         <v>1026</v>
       </c>
+      <c r="F91" s="1" t="s">
+        <v>1058</v>
+      </c>
       <c r="T91" s="41"/>
       <c r="U91" s="41"/>
       <c r="V91" s="41"/>
@@ -9246,6 +9252,9 @@
       <c r="L120" s="6" t="s">
         <v>1020</v>
       </c>
+      <c r="M120" s="1" t="s">
+        <v>1058</v>
+      </c>
       <c r="T120" s="41"/>
       <c r="U120" s="41"/>
       <c r="V120" s="41"/>
@@ -11002,6 +11011,9 @@
       </c>
       <c r="Q159" s="6" t="s">
         <v>1007</v>
+      </c>
+      <c r="R159" s="1" t="s">
+        <v>1058</v>
       </c>
       <c r="T159" s="41"/>
       <c r="U159" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -9453,16 +9453,16 @@
       <c r="A125" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B125" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C125" s="10" t="s">
+      <c r="B125" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C125" s="45" t="s">
         <v>639</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D125" s="45" t="s">
         <v>640</v>
       </c>
-      <c r="E125" s="13" t="s">
+      <c r="E125" s="45" t="s">
         <v>641</v>
       </c>
       <c r="F125" s="6" t="s">

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -1943,9 +1943,6 @@
     <t>Warlord</t>
   </si>
   <si>
-    <t>Ironscale</t>
-  </si>
-  <si>
     <t>Boneclaw</t>
   </si>
   <si>
@@ -3201,6 +3198,9 @@
   </si>
   <si>
     <t>Warhound</t>
+  </si>
+  <si>
+    <t>Shyvana Ironscale</t>
   </si>
 </sst>
 </file>
@@ -3945,43 +3945,43 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B2" s="23" t="s">
+        <v>784</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>785</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="E2" s="26" t="s">
         <v>787</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="27" t="s">
         <v>788</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="G2" s="28" t="s">
         <v>789</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="H2" s="29" t="s">
         <v>790</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="I2" s="30" t="s">
         <v>791</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="31" t="s">
+        <v>793</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>794</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M2" s="34" t="s">
         <v>792</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>794</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>795</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>1055</v>
-      </c>
-      <c r="M2" s="34" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -4036,7 +4036,7 @@
         <v>161</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>162</v>
@@ -4048,13 +4048,13 @@
         <v>500</v>
       </c>
       <c r="K5" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="L5" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>919</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="Q5" s="37"/>
       <c r="T5" s="37"/>
@@ -4097,7 +4097,7 @@
         <v>171</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>172</v>
@@ -4115,19 +4115,19 @@
         <v>278</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="S6" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="T6" s="48" t="s">
         <v>969</v>
       </c>
-      <c r="T6" s="48" t="s">
-        <v>970</v>
-      </c>
       <c r="U6" s="44" t="s">
+        <v>1032</v>
+      </c>
+      <c r="V6" s="47" t="s">
         <v>1033</v>
-      </c>
-      <c r="V6" s="47" t="s">
-        <v>1034</v>
       </c>
       <c r="W6" s="2"/>
     </row>
@@ -4166,7 +4166,7 @@
         <v>171</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>183</v>
@@ -4178,22 +4178,22 @@
         <v>175</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>170</v>
       </c>
       <c r="R7" s="9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>276</v>
       </c>
       <c r="T7" s="42" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="U7" s="47" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="V7" s="42" t="s">
         <v>173</v>
@@ -4202,19 +4202,19 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="T8" s="41"/>
       <c r="U8" s="41"/>
@@ -4279,13 +4279,13 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>996</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>997</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="45"/>
@@ -4346,13 +4346,13 @@
         <v>206</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="T11" s="41"/>
       <c r="U11" s="41"/>
@@ -4394,10 +4394,10 @@
         <v>213</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N12" s="5" t="s">
         <v>162</v>
@@ -4433,7 +4433,7 @@
         <v>219</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>220</v>
@@ -4454,16 +4454,16 @@
         <v>197</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="T13" s="41"/>
       <c r="U13" s="41"/>
@@ -4484,16 +4484,16 @@
         <v>197</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>173</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="T14" s="41"/>
       <c r="U14" s="41"/>
@@ -4532,7 +4532,7 @@
         <v>183</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>231</v>
@@ -4547,16 +4547,16 @@
         <v>276</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>509</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="T15" s="47" t="s">
         <v>177</v>
@@ -4586,13 +4586,13 @@
         <v>235</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="T16" s="41"/>
       <c r="U16" s="41"/>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>157</v>
@@ -4642,10 +4642,10 @@
         <v>172</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="T18" s="41"/>
       <c r="U18" s="41"/>
@@ -4672,13 +4672,13 @@
         <v>240</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>430</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>173</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>157</v>
@@ -4699,10 +4699,10 @@
         <v>248</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="T20" s="41"/>
       <c r="U20" s="41"/>
@@ -4756,10 +4756,10 @@
         <v>162</v>
       </c>
       <c r="P21" s="13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="T21" s="41"/>
       <c r="U21" s="41"/>
@@ -4801,13 +4801,13 @@
         <v>335</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="T22" s="41"/>
       <c r="U22" s="41"/>
@@ -4843,7 +4843,7 @@
         <v>273</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="T23" s="41"/>
       <c r="U23" s="41"/>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>931</v>
-      </c>
       <c r="D24" s="13" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>274</v>
@@ -4909,28 +4909,28 @@
         <v>169</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>274</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="S25" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="T25" s="47" t="s">
         <v>1001</v>
-      </c>
-      <c r="T25" s="47" t="s">
-        <v>1002</v>
       </c>
       <c r="U25" s="44" t="s">
         <v>432</v>
@@ -4958,16 +4958,16 @@
         <v>278</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="I26" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>897</v>
-      </c>
       <c r="J26" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="T26" s="41"/>
       <c r="U26" s="41"/>
@@ -5006,7 +5006,7 @@
         <v>326</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="T27" s="41"/>
       <c r="U27" s="41"/>
@@ -5045,13 +5045,13 @@
         <v>430</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="T28" s="41"/>
       <c r="U28" s="41"/>
@@ -5096,7 +5096,7 @@
         <v>240</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="T29" s="41"/>
       <c r="U29" s="41"/>
@@ -5138,19 +5138,19 @@
         <v>197</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>173</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q30" s="6" t="s">
         <v>312</v>
@@ -5189,25 +5189,25 @@
         <v>307</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>432</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>429</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="T31" s="41"/>
       <c r="U31" s="41"/>
@@ -5252,13 +5252,13 @@
         <v>335</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P32" s="11" t="s">
         <v>162</v>
@@ -5306,7 +5306,7 @@
         <v>322</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="T33" s="41"/>
       <c r="U33" s="41"/>
@@ -5342,19 +5342,19 @@
         <v>272</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>170</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="T34" s="41"/>
       <c r="U34" s="41"/>
@@ -5387,13 +5387,13 @@
         <v>326</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>276</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="T35" s="41"/>
       <c r="U35" s="41"/>
@@ -5426,7 +5426,7 @@
         <v>171</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="J36" s="10" t="s">
         <v>265</v>
@@ -5441,13 +5441,13 @@
         <v>173</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>232</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="T36" s="41"/>
       <c r="U36" s="41"/>
@@ -5504,25 +5504,25 @@
         <v>339</v>
       </c>
       <c r="Q37" s="10" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="S37" s="40" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="T37" s="43" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="U37" s="44" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="V37" s="49" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="W37" s="50" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
@@ -5560,13 +5560,13 @@
         <v>347</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>161</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="T38" s="41"/>
       <c r="U38" s="41"/>
@@ -5611,16 +5611,16 @@
         <v>197</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="N39" s="10" t="s">
         <v>326</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="Q39" s="10" t="s">
         <v>307</v>
@@ -5665,7 +5665,7 @@
         <v>359</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>360</v>
@@ -5674,7 +5674,7 @@
         <v>240</v>
       </c>
       <c r="N40" s="9" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="T40" s="41"/>
       <c r="U40" s="41"/>
@@ -5713,10 +5713,10 @@
         <v>365</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="T41" s="41"/>
       <c r="U41" s="41"/>
@@ -5761,7 +5761,7 @@
         <v>373</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="N42" s="13" t="s">
         <v>183</v>
@@ -5812,19 +5812,19 @@
         <v>312</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>274</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="Q43" s="10" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="R43" s="9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="T43" s="41"/>
       <c r="U43" s="41"/>
@@ -5848,7 +5848,7 @@
         <v>239</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>222</v>
@@ -5863,10 +5863,10 @@
         <v>172</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T44" s="41"/>
       <c r="U44" s="41"/>
@@ -5920,7 +5920,7 @@
         <v>232</v>
       </c>
       <c r="P45" s="13" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="T45" s="41"/>
       <c r="U45" s="41"/>
@@ -5965,13 +5965,13 @@
         <v>393</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="T46" s="41"/>
       <c r="U46" s="41"/>
@@ -5989,16 +5989,16 @@
         <v>252</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>307</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="T47" s="41"/>
       <c r="U47" s="41"/>
@@ -6043,7 +6043,7 @@
         <v>278</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>224</v>
@@ -6082,10 +6082,10 @@
         <v>273</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="T49" s="41"/>
       <c r="U49" s="41"/>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>173</v>
@@ -6127,10 +6127,10 @@
         <v>405</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="T51" s="41"/>
       <c r="U51" s="41"/>
@@ -6169,19 +6169,19 @@
         <v>183</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="L52" s="10" t="s">
         <v>232</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="O52" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>173</v>
@@ -6205,7 +6205,7 @@
         <v>301</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>240</v>
@@ -6259,16 +6259,16 @@
         <v>307</v>
       </c>
       <c r="N54" s="8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="O54" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="P54" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="P54" s="8" t="s">
-        <v>884</v>
-      </c>
       <c r="Q54" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="T54" s="41"/>
       <c r="U54" s="41"/>
@@ -6316,16 +6316,16 @@
         <v>197</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="O55" s="8" t="s">
         <v>224</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="Q55" s="8" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="T55" s="41"/>
       <c r="U55" s="41"/>
@@ -6376,13 +6376,13 @@
         <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="P56" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>183</v>
@@ -6418,22 +6418,22 @@
         <v>266</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K57" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="L57" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="L57" s="8" t="s">
-        <v>982</v>
-      </c>
       <c r="M57" s="6" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="T57" s="41"/>
       <c r="U57" s="41"/>
@@ -6469,16 +6469,16 @@
         <v>431</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N58" s="8" t="s">
         <v>278</v>
@@ -6520,22 +6520,22 @@
         <v>230</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="P59" s="11" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="T59" s="41"/>
       <c r="U59" s="41"/>
@@ -6556,7 +6556,7 @@
         <v>171</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>277</v>
@@ -6568,28 +6568,28 @@
         <v>175</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="K60" s="8" t="s">
         <v>170</v>
       </c>
       <c r="L60" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="N60" s="10" t="s">
         <v>289</v>
       </c>
       <c r="O60" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="P60" s="8" t="s">
         <v>969</v>
-      </c>
-      <c r="P60" s="8" t="s">
-        <v>970</v>
       </c>
       <c r="T60" s="41"/>
       <c r="U60" s="41"/>
@@ -6607,7 +6607,7 @@
         <v>161</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>192</v>
@@ -6616,7 +6616,7 @@
         <v>191</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>440</v>
@@ -6667,10 +6667,10 @@
         <v>313</v>
       </c>
       <c r="N62" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="P62" s="10" t="s">
         <v>177</v>
@@ -6712,7 +6712,7 @@
         <v>177</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K63" s="8" t="s">
         <v>172</v>
@@ -6754,10 +6754,10 @@
         <v>194</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="T64" s="41"/>
       <c r="U64" s="41"/>
@@ -6814,19 +6814,19 @@
         <v>232</v>
       </c>
       <c r="Q65" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="R65" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="R65" s="7" t="s">
-        <v>908</v>
-      </c>
       <c r="S65" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="T65" s="48" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="U65" s="48" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="V65" s="41"/>
       <c r="W65" s="2"/>
@@ -6872,19 +6872,19 @@
         <v>260</v>
       </c>
       <c r="N66" s="11" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P66" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="Q66" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="R66" s="8" t="s">
         <v>894</v>
-      </c>
-      <c r="R66" s="8" t="s">
-        <v>895</v>
       </c>
       <c r="S66" s="7" t="s">
         <v>173</v>
@@ -6911,13 +6911,13 @@
         <v>224</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>274</v>
@@ -6989,7 +6989,7 @@
         <v>289</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H69" s="11" t="s">
         <v>163</v>
@@ -6998,7 +6998,7 @@
         <v>556</v>
       </c>
       <c r="J69" s="8" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="T69" s="41"/>
       <c r="U69" s="41"/>
@@ -7022,19 +7022,19 @@
         <v>173</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="T70" s="41"/>
       <c r="U70" s="41"/>
@@ -7058,7 +7058,7 @@
         <v>191</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="T71" s="41"/>
       <c r="U71" s="41"/>
@@ -7109,7 +7109,7 @@
         <v>484</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="P72" s="11" t="s">
         <v>430</v>
@@ -7125,19 +7125,19 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>893</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C73" s="10" t="s">
+      <c r="D73" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>895</v>
-      </c>
       <c r="E73" s="11" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="T73" s="41"/>
       <c r="U73" s="41"/>
@@ -7176,10 +7176,10 @@
         <v>276</v>
       </c>
       <c r="K74" s="11" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>335</v>
@@ -7188,7 +7188,7 @@
         <v>326</v>
       </c>
       <c r="O74" s="8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="T74" s="41"/>
       <c r="U74" s="41"/>
@@ -7233,7 +7233,7 @@
         <v>224</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="N75" s="11" t="s">
         <v>373</v>
@@ -7242,19 +7242,19 @@
         <v>235</v>
       </c>
       <c r="P75" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="Q75" s="13" t="s">
+        <v>947</v>
+      </c>
+      <c r="R75" s="11" t="s">
         <v>948</v>
       </c>
-      <c r="R75" s="11" t="s">
-        <v>949</v>
-      </c>
       <c r="S75" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T75" s="43" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="U75" s="41"/>
       <c r="V75" s="41"/>
@@ -7301,7 +7301,7 @@
         <v>431</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>335</v>
@@ -7310,13 +7310,13 @@
         <v>232</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="S76" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="T76" s="41"/>
       <c r="U76" s="41"/>
@@ -7340,13 +7340,13 @@
         <v>430</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="T77" s="41"/>
       <c r="U77" s="41"/>
@@ -7376,16 +7376,16 @@
         <v>429</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I78" s="12" t="s">
         <v>252</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="T78" s="41"/>
       <c r="U78" s="41"/>
@@ -7421,7 +7421,7 @@
         <v>272</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>162</v>
@@ -7430,16 +7430,16 @@
         <v>278</v>
       </c>
       <c r="M79" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="O79" s="11" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="P79" s="7" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="T79" s="41"/>
       <c r="U79" s="41"/>
@@ -7481,13 +7481,13 @@
         <v>252</v>
       </c>
       <c r="L80" s="13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M80" s="13" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O80" s="9" t="s">
         <v>278</v>
@@ -7535,7 +7535,7 @@
         <v>274</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N81" s="6" t="s">
         <v>429</v>
@@ -7547,25 +7547,25 @@
         <v>252</v>
       </c>
       <c r="Q81" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R81" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="S81" s="9" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="T81" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="U81" s="47" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V81" s="48" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="W81" s="53" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
@@ -7603,13 +7603,13 @@
         <v>289</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M82" s="13" t="s">
         <v>373</v>
       </c>
       <c r="N82" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>556</v>
@@ -7660,13 +7660,13 @@
         <v>335</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="T83" s="41"/>
       <c r="U83" s="41"/>
@@ -7708,10 +7708,10 @@
         <v>240</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="T84" s="41"/>
       <c r="U84" s="41"/>
@@ -7765,13 +7765,13 @@
         <v>173</v>
       </c>
       <c r="P85" s="13" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="Q85" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="R85" s="10" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="T85" s="41"/>
       <c r="U85" s="41"/>
@@ -7780,16 +7780,16 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>1018</v>
-      </c>
       <c r="D86" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E86" s="45"/>
       <c r="F86" s="45"/>
@@ -7811,16 +7811,16 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>439</v>
@@ -7877,7 +7877,7 @@
         <v>326</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="Q88" s="8" t="s">
         <v>313</v>
@@ -7886,16 +7886,16 @@
         <v>609</v>
       </c>
       <c r="S88" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="T88" s="44" t="s">
         <v>904</v>
       </c>
-      <c r="T88" s="44" t="s">
-        <v>905</v>
-      </c>
       <c r="U88" s="44" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="V88" s="44" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="W88" s="51" t="s">
         <v>307</v>
@@ -7930,19 +7930,19 @@
         <v>183</v>
       </c>
       <c r="J89" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>232</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="T89" s="41"/>
       <c r="U89" s="41"/>
@@ -7990,22 +7990,22 @@
         <v>440</v>
       </c>
       <c r="N90" s="7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="O90" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="P90" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R90" s="5" t="s">
         <v>173</v>
       </c>
       <c r="S90" s="6" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="T90" s="41"/>
       <c r="U90" s="41"/>
@@ -8014,22 +8014,22 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>183</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T91" s="41"/>
       <c r="U91" s="41"/>
@@ -8074,16 +8074,16 @@
         <v>252</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N92" s="8" t="s">
         <v>276</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="P92" s="8" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="T92" s="41"/>
       <c r="U92" s="41"/>
@@ -8128,13 +8128,13 @@
         <v>252</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="N93" s="8" t="s">
         <v>224</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="T93" s="41"/>
       <c r="U93" s="41"/>
@@ -8155,7 +8155,7 @@
         <v>558</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>388</v>
@@ -8170,16 +8170,16 @@
         <v>430</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="M94" s="8" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="T94" s="41"/>
       <c r="U94" s="41"/>
@@ -8200,7 +8200,7 @@
         <v>170</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F95" s="13" t="s">
         <v>430</v>
@@ -8209,13 +8209,13 @@
         <v>326</v>
       </c>
       <c r="H95" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="J95" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="T95" s="41"/>
       <c r="U95" s="41"/>
@@ -8266,13 +8266,13 @@
         <v>431</v>
       </c>
       <c r="O96" s="11" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="P96" s="13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="Q96" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>173</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>157</v>
@@ -8296,7 +8296,7 @@
         <v>276</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="T97" s="41"/>
       <c r="U97" s="41"/>
@@ -8329,16 +8329,16 @@
         <v>566</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="J98" s="6" t="s">
         <v>194</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L98" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="T98" s="41"/>
       <c r="U98" s="41"/>
@@ -8380,13 +8380,13 @@
         <v>252</v>
       </c>
       <c r="L99" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="T99" s="41"/>
       <c r="U99" s="41"/>
@@ -8425,10 +8425,10 @@
         <v>260</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="L100" s="13" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M100" s="10" t="s">
         <v>177</v>
@@ -8473,13 +8473,13 @@
         <v>273</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="M101" s="8" t="s">
         <v>170</v>
       </c>
       <c r="N101" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T101" s="41"/>
       <c r="U101" s="41"/>
@@ -8503,10 +8503,10 @@
         <v>252</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="T102" s="41"/>
       <c r="U102" s="41"/>
@@ -8551,13 +8551,13 @@
         <v>313</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="O103" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="T103" s="41"/>
       <c r="U103" s="41"/>
@@ -8605,7 +8605,7 @@
         <v>326</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="O104" s="10" t="s">
         <v>432</v>
@@ -8635,28 +8635,28 @@
         <v>339</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K105" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L105" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="M105" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N105" s="11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T105" s="41"/>
       <c r="U105" s="41"/>
@@ -8677,22 +8677,22 @@
         <v>184</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F106" s="13" t="s">
         <v>307</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H106" s="7" t="s">
         <v>509</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="T106" s="41"/>
       <c r="U106" s="41"/>
@@ -8758,16 +8758,16 @@
         <v>278</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="K108" s="6" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L108" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="M108" s="10" t="s">
         <v>943</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>944</v>
       </c>
       <c r="N108" s="11" t="s">
         <v>274</v>
@@ -8815,7 +8815,7 @@
         <v>240</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="T109" s="41"/>
       <c r="U109" s="41"/>
@@ -8842,7 +8842,7 @@
         <v>172</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="T110" s="41"/>
       <c r="U110" s="41"/>
@@ -8866,7 +8866,7 @@
         <v>232</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="T111" s="41"/>
       <c r="U111" s="41"/>
@@ -8875,25 +8875,25 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>839</v>
       </c>
-      <c r="B112" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>840</v>
-      </c>
       <c r="D112" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E112" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="F112" s="10" t="s">
         <v>932</v>
       </c>
-      <c r="F112" s="10" t="s">
-        <v>933</v>
-      </c>
       <c r="G112" s="6" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="T112" s="41"/>
       <c r="U112" s="41"/>
@@ -8947,10 +8947,10 @@
         <v>440</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="Q113" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="T113" s="41"/>
       <c r="U113" s="41"/>
@@ -8983,10 +8983,10 @@
         <v>417</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="J114" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="T114" s="41"/>
       <c r="U114" s="41"/>
@@ -9010,7 +9010,7 @@
         <v>609</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G115" s="11" t="s">
         <v>610</v>
@@ -9019,7 +9019,7 @@
         <v>169</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="J115" s="6" t="s">
         <v>440</v>
@@ -9031,22 +9031,22 @@
         <v>611</v>
       </c>
       <c r="M115" s="8" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="N115" s="9" t="s">
         <v>173</v>
       </c>
       <c r="O115" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P115" s="11" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="Q115" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="R115" s="8" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="T115" s="41"/>
       <c r="U115" s="41"/>
@@ -9076,7 +9076,7 @@
         <v>252</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="T116" s="41"/>
       <c r="U116" s="41"/>
@@ -9121,7 +9121,7 @@
         <v>192</v>
       </c>
       <c r="M117" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="N117" s="11" t="s">
         <v>417</v>
@@ -9154,10 +9154,10 @@
         <v>232</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H118" s="10" t="s">
         <v>393</v>
@@ -9226,7 +9226,7 @@
         <v>184</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>232</v>
@@ -9238,7 +9238,7 @@
         <v>500</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="I120" s="6" t="s">
         <v>326</v>
@@ -9247,13 +9247,13 @@
         <v>170</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M120" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T120" s="41"/>
       <c r="U120" s="41"/>
@@ -9268,31 +9268,31 @@
         <v>157</v>
       </c>
       <c r="C121" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="D121" s="9" t="s">
         <v>797</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="E121" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="E121" s="6" t="s">
-        <v>799</v>
-      </c>
       <c r="F121" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="H121" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="H121" s="8" t="s">
-        <v>877</v>
-      </c>
       <c r="I121" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="J121" s="11" t="s">
         <v>170</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="L121" s="6" t="s">
         <v>432</v>
@@ -9316,7 +9316,7 @@
         <v>628</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>273</v>
@@ -9328,16 +9328,16 @@
         <v>173</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="K122" s="8" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L122" s="9" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="T122" s="41"/>
       <c r="U122" s="41"/>
@@ -9379,22 +9379,22 @@
         <v>483</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M123" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N123" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="O123" s="13" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="Q123" s="12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="T123" s="41"/>
       <c r="U123" s="41"/>
@@ -9436,13 +9436,13 @@
         <v>339</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="M124" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="T124" s="41"/>
       <c r="U124" s="41"/>
@@ -9457,19 +9457,19 @@
         <v>157</v>
       </c>
       <c r="C125" s="45" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D125" s="45" t="s">
         <v>639</v>
       </c>
-      <c r="D125" s="45" t="s">
+      <c r="E125" s="45" t="s">
         <v>640</v>
       </c>
-      <c r="E125" s="45" t="s">
+      <c r="F125" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="F125" s="6" t="s">
-        <v>642</v>
-      </c>
       <c r="G125" s="11" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H125" s="13" t="s">
         <v>222</v>
@@ -9478,7 +9478,7 @@
         <v>313</v>
       </c>
       <c r="J125" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T125" s="41"/>
       <c r="U125" s="41"/>
@@ -9493,19 +9493,19 @@
         <v>157</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D126" s="21" t="s">
         <v>194</v>
       </c>
       <c r="E126" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="F126" s="13" t="s">
         <v>644</v>
       </c>
-      <c r="F126" s="13" t="s">
+      <c r="G126" s="11" t="s">
         <v>645</v>
-      </c>
-      <c r="G126" s="11" t="s">
-        <v>646</v>
       </c>
       <c r="H126" s="11" t="s">
         <v>239</v>
@@ -9514,10 +9514,10 @@
         <v>605</v>
       </c>
       <c r="J126" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="K126" s="6" t="s">
         <v>647</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>648</v>
       </c>
       <c r="L126" s="10" t="s">
         <v>266</v>
@@ -9526,7 +9526,7 @@
         <v>240</v>
       </c>
       <c r="N126" s="8" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="T126" s="41"/>
       <c r="U126" s="41"/>
@@ -9544,16 +9544,16 @@
         <v>194</v>
       </c>
       <c r="D127" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="E127" s="10" t="s">
+      <c r="F127" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="G127" s="9" t="s">
         <v>651</v>
-      </c>
-      <c r="G127" s="9" t="s">
-        <v>652</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>521</v>
@@ -9565,10 +9565,10 @@
         <v>232</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L127" s="8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="T127" s="41"/>
       <c r="U127" s="41"/>
@@ -9583,22 +9583,22 @@
         <v>157</v>
       </c>
       <c r="C128" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="D128" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="E128" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="E128" s="13" t="s">
+      <c r="F128" s="10" t="s">
         <v>655</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>656</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>421</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I128" s="10" t="s">
         <v>388</v>
@@ -9607,10 +9607,10 @@
         <v>162</v>
       </c>
       <c r="K128" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="L128" s="10" t="s">
         <v>658</v>
-      </c>
-      <c r="L128" s="10" t="s">
-        <v>659</v>
       </c>
       <c r="M128" s="7" t="s">
         <v>161</v>
@@ -9619,22 +9619,22 @@
         <v>163</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>499</v>
       </c>
       <c r="Q128" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="R128" s="7" t="s">
         <v>899</v>
       </c>
-      <c r="R128" s="7" t="s">
-        <v>900</v>
-      </c>
       <c r="S128" s="9" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="T128" s="47" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="U128" s="41"/>
       <c r="V128" s="41"/>
@@ -9648,19 +9648,19 @@
         <v>157</v>
       </c>
       <c r="C129" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D129" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="D129" s="8" t="s">
+      <c r="E129" s="11" t="s">
         <v>661</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>662</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>417</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H129" s="13" t="s">
         <v>312</v>
@@ -9672,13 +9672,13 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="9" t="s">
         <v>947</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>948</v>
       </c>
       <c r="D130" s="13" t="s">
         <v>478</v>
@@ -9696,22 +9696,22 @@
         <v>157</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D131" s="11" t="s">
         <v>444</v>
       </c>
       <c r="E131" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="F131" s="10" t="s">
         <v>665</v>
-      </c>
-      <c r="F131" s="10" t="s">
-        <v>666</v>
       </c>
       <c r="G131" s="13" t="s">
         <v>169</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I131" s="9" t="s">
         <v>221</v>
@@ -9723,25 +9723,25 @@
         <v>339</v>
       </c>
       <c r="L131" s="13" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M131" s="9" t="s">
         <v>170</v>
       </c>
       <c r="N131" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="O131" s="7" t="s">
         <v>924</v>
-      </c>
-      <c r="O131" s="7" t="s">
-        <v>925</v>
       </c>
       <c r="P131" s="5" t="s">
         <v>162</v>
       </c>
       <c r="Q131" s="9" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="T131" s="41"/>
       <c r="U131" s="41"/>
@@ -9756,19 +9756,19 @@
         <v>157</v>
       </c>
       <c r="C132" s="10" t="s">
+        <v>667</v>
+      </c>
+      <c r="D132" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="E132" s="13" t="s">
         <v>669</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>670</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>395</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H132" s="11" t="s">
         <v>275</v>
@@ -9789,22 +9789,22 @@
         <v>224</v>
       </c>
       <c r="N132" s="7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="O132" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="P132" s="9" t="s">
         <v>173</v>
       </c>
       <c r="Q132" s="6" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="R132" s="8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="S132" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="T132" s="41"/>
       <c r="U132" s="41"/>
@@ -9819,31 +9819,31 @@
         <v>157</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>454</v>
       </c>
       <c r="E133" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="F133" s="8" t="s">
         <v>673</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>674</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>194</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I133" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J133" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="K133" s="8" t="s">
         <v>997</v>
-      </c>
-      <c r="K133" s="8" t="s">
-        <v>998</v>
       </c>
       <c r="T133" s="41"/>
       <c r="U133" s="41"/>
@@ -9867,22 +9867,22 @@
         <v>183</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G134" s="13" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J134" s="13" t="s">
         <v>289</v>
       </c>
       <c r="K134" s="9" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="T134" s="41"/>
       <c r="U134" s="41"/>
@@ -9903,7 +9903,7 @@
         <v>353</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F135" s="11" t="s">
         <v>239</v>
@@ -9918,13 +9918,13 @@
         <v>273</v>
       </c>
       <c r="J135" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K135" s="6" t="s">
         <v>326</v>
       </c>
       <c r="L135" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M135" s="9" t="s">
         <v>173</v>
@@ -9933,7 +9933,7 @@
         <v>276</v>
       </c>
       <c r="O135" s="6" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="T135" s="41"/>
       <c r="U135" s="41"/>
@@ -9948,13 +9948,13 @@
         <v>157</v>
       </c>
       <c r="C136" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="D136" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="E136" s="6" t="s">
         <v>679</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>680</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>278</v>
@@ -9990,10 +9990,10 @@
         <v>170</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="T137" s="41"/>
       <c r="U137" s="41"/>
@@ -10008,7 +10008,7 @@
         <v>157</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D138" s="13" t="s">
         <v>608</v>
@@ -10023,25 +10023,25 @@
         <v>161</v>
       </c>
       <c r="H138" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="I138" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="I138" s="11" t="s">
-        <v>683</v>
-      </c>
       <c r="J138" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>232</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="N138" s="8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="T138" s="41"/>
       <c r="U138" s="41"/>
@@ -10056,10 +10056,10 @@
         <v>157</v>
       </c>
       <c r="C139" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="D139" s="9" t="s">
         <v>684</v>
-      </c>
-      <c r="D139" s="9" t="s">
-        <v>685</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>501</v>
@@ -10068,13 +10068,13 @@
         <v>273</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H139" s="12" t="s">
         <v>252</v>
       </c>
       <c r="I139" s="10" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="T139" s="41"/>
       <c r="U139" s="41"/>
@@ -10089,13 +10089,13 @@
         <v>157</v>
       </c>
       <c r="C140" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="D140" s="10" t="s">
         <v>687</v>
       </c>
-      <c r="D140" s="10" t="s">
+      <c r="E140" s="10" t="s">
         <v>688</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>689</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>240</v>
@@ -10116,13 +10116,13 @@
         <v>360</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="M140" s="6" t="s">
         <v>173</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O140" s="10" t="s">
         <v>432</v>
@@ -10131,7 +10131,7 @@
         <v>252</v>
       </c>
       <c r="Q140" s="6" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="T140" s="41"/>
       <c r="U140" s="41"/>
@@ -10146,10 +10146,10 @@
         <v>157</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>161</v>
@@ -10167,7 +10167,7 @@
         <v>272</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K141" s="11" t="s">
         <v>373</v>
@@ -10176,19 +10176,19 @@
         <v>173</v>
       </c>
       <c r="M141" s="11" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N141" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="O141" s="8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q141" s="10" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="T141" s="41"/>
       <c r="U141" s="41"/>
@@ -10203,22 +10203,22 @@
         <v>157</v>
       </c>
       <c r="C142" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="D142" s="6" t="s">
         <v>692</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="E142" s="11" t="s">
         <v>693</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="F142" s="13" t="s">
         <v>694</v>
       </c>
-      <c r="F142" s="13" t="s">
+      <c r="G142" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="G142" s="11" t="s">
+      <c r="H142" s="11" t="s">
         <v>696</v>
-      </c>
-      <c r="H142" s="11" t="s">
-        <v>697</v>
       </c>
       <c r="I142" s="6" t="s">
         <v>403</v>
@@ -10230,10 +10230,10 @@
         <v>358</v>
       </c>
       <c r="L142" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="M142" s="13" t="s">
         <v>698</v>
-      </c>
-      <c r="M142" s="13" t="s">
-        <v>699</v>
       </c>
       <c r="N142" s="8" t="s">
         <v>194</v>
@@ -10245,10 +10245,10 @@
         <v>173</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="R142" s="10" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="T142" s="41"/>
       <c r="U142" s="41"/>
@@ -10263,16 +10263,16 @@
         <v>157</v>
       </c>
       <c r="C143" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="D143" s="13" t="s">
         <v>700</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>701</v>
       </c>
       <c r="E143" s="11" t="s">
         <v>438</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G143" s="11" t="s">
         <v>521</v>
@@ -10281,10 +10281,10 @@
         <v>260</v>
       </c>
       <c r="I143" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="T143" s="41"/>
       <c r="U143" s="41"/>
@@ -10299,16 +10299,16 @@
         <v>157</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D144" s="10" t="s">
         <v>595</v>
       </c>
       <c r="E144" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="F144" s="13" t="s">
         <v>704</v>
-      </c>
-      <c r="F144" s="13" t="s">
-        <v>705</v>
       </c>
       <c r="G144" s="11" t="s">
         <v>371</v>
@@ -10323,7 +10323,7 @@
         <v>311</v>
       </c>
       <c r="K144" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L144" s="8" t="s">
         <v>161</v>
@@ -10335,7 +10335,7 @@
         <v>162</v>
       </c>
       <c r="O144" s="9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="T144" s="41"/>
       <c r="U144" s="41"/>
@@ -10353,10 +10353,10 @@
         <v>421</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>328</v>
@@ -10365,16 +10365,16 @@
         <v>232</v>
       </c>
       <c r="H145" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="I145" s="10" t="s">
         <v>708</v>
-      </c>
-      <c r="I145" s="10" t="s">
-        <v>709</v>
       </c>
       <c r="J145" s="13" t="s">
         <v>453</v>
       </c>
       <c r="K145" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L145" s="6" t="s">
         <v>161</v>
@@ -10389,7 +10389,7 @@
         <v>431</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q145" s="12" t="s">
         <v>252</v>
@@ -10410,13 +10410,13 @@
         <v>157</v>
       </c>
       <c r="C146" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="D146" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="E146" s="13" t="s">
         <v>712</v>
-      </c>
-      <c r="E146" s="13" t="s">
-        <v>713</v>
       </c>
       <c r="F146" s="10" t="s">
         <v>264</v>
@@ -10425,7 +10425,7 @@
         <v>254</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I146" s="13" t="s">
         <v>605</v>
@@ -10434,10 +10434,10 @@
         <v>358</v>
       </c>
       <c r="K146" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="L146" s="10" t="s">
         <v>715</v>
-      </c>
-      <c r="L146" s="10" t="s">
-        <v>716</v>
       </c>
       <c r="M146" s="11" t="s">
         <v>260</v>
@@ -10446,7 +10446,7 @@
         <v>232</v>
       </c>
       <c r="O146" s="10" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="P146" s="13" t="s">
         <v>273</v>
@@ -10464,22 +10464,22 @@
         <v>157</v>
       </c>
       <c r="C147" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="D147" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="D147" s="9" t="s">
+      <c r="E147" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>719</v>
       </c>
       <c r="F147" s="12" t="s">
         <v>245</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="T147" s="41"/>
       <c r="U147" s="41"/>
@@ -10494,7 +10494,7 @@
         <v>157</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D148" s="10" t="s">
         <v>573</v>
@@ -10506,13 +10506,13 @@
         <v>232</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I148" s="12" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="T148" s="41"/>
       <c r="U148" s="41"/>
@@ -10527,7 +10527,7 @@
         <v>157</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>258</v>
@@ -10539,7 +10539,7 @@
         <v>230</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>289</v>
@@ -10551,7 +10551,7 @@
         <v>177</v>
       </c>
       <c r="K149" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L149" s="8" t="s">
         <v>183</v>
@@ -10560,16 +10560,16 @@
         <v>232</v>
       </c>
       <c r="N149" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O149" s="8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>173</v>
       </c>
       <c r="Q149" s="6" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T149" s="41"/>
       <c r="U149" s="41"/>
@@ -10584,10 +10584,10 @@
         <v>157</v>
       </c>
       <c r="C150" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="D150" s="12" t="s">
         <v>725</v>
-      </c>
-      <c r="D150" s="12" t="s">
-        <v>726</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>260</v>
@@ -10602,7 +10602,7 @@
         <v>258</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J150" s="11" t="s">
         <v>183</v>
@@ -10611,7 +10611,7 @@
         <v>432</v>
       </c>
       <c r="L150" s="10" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M150" s="10" t="s">
         <v>173</v>
@@ -10620,19 +10620,19 @@
         <v>373</v>
       </c>
       <c r="O150" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="P150" s="12" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="Q150" s="8" t="s">
         <v>440</v>
       </c>
       <c r="R150" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="S150" s="6" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="T150" s="41"/>
       <c r="U150" s="41"/>
@@ -10647,28 +10647,28 @@
         <v>157</v>
       </c>
       <c r="C151" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="D151" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="E151" s="11" t="s">
         <v>729</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="F151" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="F151" s="12" t="s">
+      <c r="G151" s="13" t="s">
         <v>731</v>
       </c>
-      <c r="G151" s="13" t="s">
+      <c r="H151" s="13" t="s">
         <v>732</v>
       </c>
-      <c r="H151" s="13" t="s">
+      <c r="I151" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="I151" s="13" t="s">
+      <c r="J151" s="10" t="s">
         <v>734</v>
-      </c>
-      <c r="J151" s="10" t="s">
-        <v>735</v>
       </c>
       <c r="K151" s="10" t="s">
         <v>358</v>
@@ -10677,19 +10677,19 @@
         <v>172</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="N151" s="11" t="s">
         <v>240</v>
       </c>
       <c r="O151" s="12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="P151" s="13" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="Q151" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="T151" s="41"/>
       <c r="U151" s="41"/>
@@ -10719,7 +10719,7 @@
         <v>196</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="T152" s="41"/>
       <c r="U152" s="41"/>
@@ -10728,7 +10728,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>157</v>
@@ -10737,10 +10737,10 @@
         <v>440</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="T153" s="41"/>
       <c r="U153" s="41"/>
@@ -10755,7 +10755,7 @@
         <v>157</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D154" s="13" t="s">
         <v>270</v>
@@ -10764,7 +10764,7 @@
         <v>335</v>
       </c>
       <c r="F154" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G154" s="10" t="s">
         <v>238</v>
@@ -10773,25 +10773,25 @@
         <v>183</v>
       </c>
       <c r="I154" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J154" s="11" t="s">
         <v>339</v>
       </c>
       <c r="K154" s="9" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L154" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="O154" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T154" s="41"/>
       <c r="U154" s="41"/>
@@ -10809,22 +10809,22 @@
         <v>197</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>595</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="I155" s="8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="T155" s="41"/>
       <c r="U155" s="41"/>
@@ -10839,13 +10839,13 @@
         <v>157</v>
       </c>
       <c r="C156" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="D156" s="9" t="s">
         <v>740</v>
       </c>
-      <c r="D156" s="9" t="s">
+      <c r="E156" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>742</v>
       </c>
       <c r="F156" s="8" t="s">
         <v>458</v>
@@ -10857,10 +10857,10 @@
         <v>232</v>
       </c>
       <c r="I156" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="J156" s="8" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="T156" s="41"/>
       <c r="U156" s="41"/>
@@ -10878,19 +10878,19 @@
         <v>451</v>
       </c>
       <c r="D157" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="E157" s="13" t="s">
         <v>743</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>744</v>
       </c>
       <c r="F157" s="13" t="s">
         <v>254</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="I157" s="13" t="s">
         <v>174</v>
@@ -10902,16 +10902,16 @@
         <v>224</v>
       </c>
       <c r="L157" s="8" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M157" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="T157" s="41"/>
       <c r="U157" s="41"/>
@@ -10929,31 +10929,31 @@
         <v>577</v>
       </c>
       <c r="D158" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="E158" s="10" t="s">
         <v>747</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>748</v>
       </c>
       <c r="F158" s="11" t="s">
         <v>372</v>
       </c>
       <c r="G158" s="13" t="s">
+        <v>748</v>
+      </c>
+      <c r="H158" s="8" t="s">
         <v>749</v>
       </c>
-      <c r="H158" s="8" t="s">
-        <v>750</v>
-      </c>
       <c r="I158" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="J158" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="L158" s="13" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="T158" s="41"/>
       <c r="U158" s="41"/>
@@ -10968,31 +10968,31 @@
         <v>157</v>
       </c>
       <c r="C159" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="D159" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="D159" s="13" t="s">
+      <c r="E159" s="13" t="s">
         <v>752</v>
       </c>
-      <c r="E159" s="13" t="s">
+      <c r="F159" s="11" t="s">
         <v>753</v>
       </c>
-      <c r="F159" s="11" t="s">
+      <c r="G159" s="11" t="s">
         <v>754</v>
       </c>
-      <c r="G159" s="11" t="s">
+      <c r="H159" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="H159" s="8" t="s">
+      <c r="I159" s="13" t="s">
         <v>756</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>757</v>
       </c>
       <c r="J159" s="10" t="s">
         <v>191</v>
       </c>
       <c r="K159" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L159" s="10" t="s">
         <v>556</v>
@@ -11001,19 +11001,19 @@
         <v>183</v>
       </c>
       <c r="N159" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="O159" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="P159" s="6" t="s">
         <v>896</v>
       </c>
-      <c r="P159" s="6" t="s">
-        <v>897</v>
-      </c>
       <c r="Q159" s="6" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="T159" s="41"/>
       <c r="U159" s="41"/>
@@ -11028,22 +11028,22 @@
         <v>157</v>
       </c>
       <c r="C160" s="13" t="s">
+        <v>758</v>
+      </c>
+      <c r="D160" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="D160" s="9" t="s">
+      <c r="E160" s="11" t="s">
         <v>760</v>
       </c>
-      <c r="E160" s="11" t="s">
+      <c r="F160" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="G160" s="10" t="s">
         <v>761</v>
       </c>
-      <c r="F160" s="11" t="s">
-        <v>709</v>
-      </c>
-      <c r="G160" s="10" t="s">
+      <c r="H160" s="8" t="s">
         <v>762</v>
-      </c>
-      <c r="H160" s="8" t="s">
-        <v>763</v>
       </c>
       <c r="I160" s="12" t="s">
         <v>274</v>
@@ -11067,7 +11067,7 @@
         <v>157</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D161" s="8" t="s">
         <v>221</v>
@@ -11082,22 +11082,22 @@
         <v>172</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="I161" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="J161" s="8" t="s">
         <v>278</v>
       </c>
       <c r="K161" s="7" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M161" s="8" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N161" s="8" t="s">
         <v>274</v>
@@ -11115,7 +11115,7 @@
         <v>157</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D162" s="13" t="s">
         <v>481</v>
@@ -11136,10 +11136,10 @@
         <v>240</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="T162" s="41"/>
       <c r="U162" s="41"/>
@@ -11160,10 +11160,10 @@
         <v>507</v>
       </c>
       <c r="E163" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="F163" s="10" t="s">
         <v>766</v>
-      </c>
-      <c r="F163" s="10" t="s">
-        <v>767</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>238</v>
@@ -11175,7 +11175,7 @@
         <v>260</v>
       </c>
       <c r="J163" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K163" s="6" t="s">
         <v>191</v>
@@ -11184,7 +11184,7 @@
         <v>432</v>
       </c>
       <c r="M163" s="8" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="T163" s="41"/>
       <c r="U163" s="41"/>
@@ -11220,37 +11220,37 @@
         <v>184</v>
       </c>
       <c r="J164" s="10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K164" s="7" t="s">
         <v>173</v>
       </c>
       <c r="L164" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="M164" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="M164" s="5" t="s">
-        <v>814</v>
-      </c>
       <c r="N164" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="O164" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="P164" s="10" t="s">
         <v>916</v>
       </c>
-      <c r="P164" s="10" t="s">
-        <v>917</v>
-      </c>
       <c r="Q164" s="8" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="R164" s="11" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="S164" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="T164" s="44" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="U164" s="41"/>
       <c r="V164" s="41"/>
@@ -11273,28 +11273,28 @@
         <v>440</v>
       </c>
       <c r="F165" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H165" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="I165" s="9" t="s">
         <v>936</v>
-      </c>
-      <c r="I165" s="9" t="s">
-        <v>937</v>
       </c>
       <c r="J165" s="6" t="s">
         <v>232</v>
       </c>
       <c r="K165" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T165" s="41"/>
       <c r="U165" s="41"/>
@@ -11309,7 +11309,7 @@
         <v>157</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D166" s="11" t="s">
         <v>444</v>
@@ -11318,13 +11318,13 @@
         <v>258</v>
       </c>
       <c r="F166" s="13" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G166" s="13" t="s">
         <v>266</v>
       </c>
       <c r="H166" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I166" s="10" t="s">
         <v>173</v>
@@ -11342,13 +11342,13 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C167" s="10" t="s">
         <v>1032</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C167" s="10" t="s">
-        <v>1033</v>
       </c>
       <c r="D167" s="45"/>
       <c r="E167" s="45"/>
@@ -11370,28 +11370,28 @@
         <v>157</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D168" s="11" t="s">
         <v>230</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>326</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="I168" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="J168" s="10" t="s">
         <v>972</v>
-      </c>
-      <c r="J168" s="10" t="s">
-        <v>973</v>
       </c>
       <c r="K168" s="8" t="s">
         <v>224</v>
@@ -11406,13 +11406,13 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B169" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D169" s="45"/>
       <c r="E169" s="45"/>
@@ -11434,7 +11434,7 @@
         <v>157</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D170" s="13" t="s">
         <v>273</v>
@@ -11446,10 +11446,10 @@
         <v>481</v>
       </c>
       <c r="G170" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="T170" s="41"/>
       <c r="U170" s="41"/>
@@ -11464,7 +11464,7 @@
         <v>157</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D171" s="10" t="s">
         <v>192</v>
@@ -11473,37 +11473,37 @@
         <v>183</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G171" s="10" t="s">
         <v>458</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I171" s="11" t="s">
         <v>339</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K171" s="9" t="s">
         <v>335</v>
       </c>
       <c r="L171" s="10" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="M171" s="8" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="N171" s="10" t="s">
         <v>161</v>
       </c>
       <c r="O171" s="6" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="T171" s="41"/>
       <c r="U171" s="41"/>
@@ -11512,25 +11512,25 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B172" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E172" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G172" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H172" s="9" t="s">
         <v>439</v>
@@ -11548,10 +11548,10 @@
         <v>157</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E173" s="11" t="s">
         <v>273</v>
@@ -11560,7 +11560,7 @@
         <v>239</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H173" s="11" t="s">
         <v>248</v>
@@ -11575,10 +11575,10 @@
         <v>194</v>
       </c>
       <c r="L173" s="11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="M173" s="12" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="N173" s="13" t="s">
         <v>432</v>
@@ -11596,16 +11596,16 @@
         <v>157</v>
       </c>
       <c r="C174" s="13" t="s">
+        <v>777</v>
+      </c>
+      <c r="D174" s="12" t="s">
         <v>778</v>
       </c>
-      <c r="D174" s="12" t="s">
+      <c r="E174" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="E174" s="11" t="s">
+      <c r="F174" s="13" t="s">
         <v>780</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>781</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>161</v>
@@ -11614,7 +11614,7 @@
         <v>265</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J174" s="8" t="s">
         <v>278</v>
@@ -11632,7 +11632,7 @@
         <v>157</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D175" s="10" t="s">
         <v>273</v>
@@ -11644,19 +11644,19 @@
         <v>483</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H175" s="10" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="I175" s="10" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="J175" s="11" t="s">
         <v>289</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="T175" s="41"/>
       <c r="U175" s="41"/>
@@ -11671,7 +11671,7 @@
         <v>157</v>
       </c>
       <c r="C176" s="17" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D176" s="18" t="s">
         <v>526</v>
@@ -11680,25 +11680,25 @@
         <v>192</v>
       </c>
       <c r="F176" s="19" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G176" s="16" t="s">
         <v>276</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I176" s="36" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J176" s="18" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K176" s="18" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L176" s="16" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M176" s="52" t="s">
         <v>161</v>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="1064">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3201,6 +3201,21 @@
   </si>
   <si>
     <t>Shyvana Ironscale</t>
+  </si>
+  <si>
+    <t>Fried Chicken King</t>
+  </si>
+  <si>
+    <t>Bubble Bash</t>
+  </si>
+  <si>
+    <t>Prestige Money Miser</t>
+  </si>
+  <si>
+    <t>Pug Trainer</t>
+  </si>
+  <si>
+    <t>Choncc</t>
   </si>
 </sst>
 </file>
@@ -4761,6 +4776,9 @@
       <c r="Q21" s="9" t="s">
         <v>938</v>
       </c>
+      <c r="R21" s="1" t="s">
+        <v>1060</v>
+      </c>
       <c r="T21" s="41"/>
       <c r="U21" s="41"/>
       <c r="V21" s="41"/>
@@ -7944,6 +7962,9 @@
       <c r="N89" s="10" t="s">
         <v>1027</v>
       </c>
+      <c r="O89" s="1" t="s">
+        <v>1061</v>
+      </c>
       <c r="T89" s="41"/>
       <c r="U89" s="41"/>
       <c r="V89" s="41"/>
@@ -9210,6 +9231,9 @@
       <c r="N119" s="7" t="s">
         <v>162</v>
       </c>
+      <c r="O119" s="1" t="s">
+        <v>1062</v>
+      </c>
       <c r="T119" s="41"/>
       <c r="U119" s="41"/>
       <c r="V119" s="41"/>
@@ -9845,6 +9869,9 @@
       <c r="K133" s="8" t="s">
         <v>997</v>
       </c>
+      <c r="L133" s="1" t="s">
+        <v>1059</v>
+      </c>
       <c r="T133" s="41"/>
       <c r="U133" s="41"/>
       <c r="V133" s="41"/>
@@ -9965,6 +9992,9 @@
       <c r="H136" s="10" t="s">
         <v>430</v>
       </c>
+      <c r="I136" s="1" t="s">
+        <v>1063</v>
+      </c>
       <c r="T136" s="41"/>
       <c r="U136" s="41"/>
       <c r="V136" s="41"/>
@@ -10741,6 +10771,9 @@
       </c>
       <c r="E153" s="10" t="s">
         <v>1030</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="T153" s="41"/>
       <c r="U153" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="1065">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3216,6 +3216,9 @@
   </si>
   <si>
     <t>Choncc</t>
+  </si>
+  <si>
+    <t>PROJECT: Command Line</t>
   </si>
 </sst>
 </file>
@@ -7791,6 +7794,9 @@
       <c r="R85" s="10" t="s">
         <v>947</v>
       </c>
+      <c r="S85" s="1" t="s">
+        <v>1064</v>
+      </c>
       <c r="T85" s="41"/>
       <c r="U85" s="41"/>
       <c r="V85" s="41"/>
@@ -9660,7 +9666,9 @@
       <c r="T128" s="47" t="s">
         <v>993</v>
       </c>
-      <c r="U128" s="41"/>
+      <c r="U128" s="41" t="s">
+        <v>183</v>
+      </c>
       <c r="V128" s="41"/>
       <c r="W128" s="2"/>
     </row>
@@ -10945,6 +10953,9 @@
       </c>
       <c r="O157" s="10" t="s">
         <v>1014</v>
+      </c>
+      <c r="P157" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="T157" s="41"/>
       <c r="U157" s="41"/>
@@ -11484,6 +11495,9 @@
       <c r="H170" s="13" t="s">
         <v>952</v>
       </c>
+      <c r="I170" s="1" t="s">
+        <v>252</v>
+      </c>
       <c r="T170" s="41"/>
       <c r="U170" s="41"/>
       <c r="V170" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="1068">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3219,6 +3219,15 @@
   </si>
   <si>
     <t>PROJECT: Command Line</t>
+  </si>
+  <si>
+    <t>Pandemonium</t>
+  </si>
+  <si>
+    <t>Demoncursed</t>
+  </si>
+  <si>
+    <t>Prestige Pandemonium</t>
   </si>
 </sst>
 </file>
@@ -4483,7 +4492,9 @@
       <c r="S13" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="T13" s="41"/>
+      <c r="T13" s="41" t="s">
+        <v>1065</v>
+      </c>
       <c r="U13" s="41"/>
       <c r="V13" s="41"/>
       <c r="W13" s="2"/>
@@ -7056,6 +7067,9 @@
       </c>
       <c r="J70" s="6" t="s">
         <v>996</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>1065</v>
       </c>
       <c r="T70" s="41"/>
       <c r="U70" s="41"/>
@@ -9426,6 +9440,9 @@
       <c r="Q123" s="12" t="s">
         <v>1026</v>
       </c>
+      <c r="R123" s="1" t="s">
+        <v>1067</v>
+      </c>
       <c r="T123" s="41"/>
       <c r="U123" s="41"/>
       <c r="V123" s="41"/>
@@ -10672,7 +10689,9 @@
       <c r="S150" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="T150" s="41"/>
+      <c r="T150" s="41" t="s">
+        <v>1066</v>
+      </c>
       <c r="U150" s="41"/>
       <c r="V150" s="41"/>
       <c r="W150" s="2"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="1068">
   <si>
     <t>Aatrox</t>
   </si>
@@ -6245,6 +6245,9 @@
       <c r="G53" s="10" t="s">
         <v>173</v>
       </c>
+      <c r="H53" s="1" t="s">
+        <v>970</v>
+      </c>
       <c r="T53" s="41"/>
       <c r="U53" s="41"/>
       <c r="V53" s="41"/>
@@ -8765,6 +8768,9 @@
       <c r="H107" s="10" t="s">
         <v>170</v>
       </c>
+      <c r="I107" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="T107" s="41"/>
       <c r="U107" s="41"/>
       <c r="V107" s="41"/>
